--- a/apostas/Bolao_Copa2026_TurimMFO - Consolidada.xlsx
+++ b/apostas/Bolao_Copa2026_TurimMFO - Consolidada.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EO8"/>
+  <dimension ref="A1:EO9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2026,20 +2026,20 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Gustavo Marini</t>
+          <t>Ana Leticia Xavier</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
         <v>2</v>
@@ -2051,28 +2051,28 @@
         <v>2</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
         <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>3</v>
@@ -2084,70 +2084,70 @@
         <v>2</v>
       </c>
       <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
+      </c>
+      <c r="V4" t="n">
+        <v>2</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF4" t="n">
         <v>4</v>
       </c>
-      <c r="U4" t="n">
-        <v>2</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1</v>
-      </c>
-      <c r="X4" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>6</v>
-      </c>
       <c r="AG4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ4" t="n">
         <v>3</v>
       </c>
       <c r="AK4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM4" t="n">
         <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AP4" t="n">
         <v>1</v>
@@ -2165,25 +2165,25 @@
         <v>1</v>
       </c>
       <c r="AU4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AX4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AY4" t="n">
         <v>0</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB4" t="n">
         <v>3</v>
@@ -2195,40 +2195,40 @@
         <v>2</v>
       </c>
       <c r="BE4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BG4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BH4" t="n">
         <v>0</v>
       </c>
       <c r="BI4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BJ4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BK4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BL4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BM4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BN4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BO4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BP4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ4" t="n">
         <v>2</v>
@@ -2240,49 +2240,49 @@
         <v>1</v>
       </c>
       <c r="BT4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BV4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BW4" t="n">
         <v>1</v>
       </c>
       <c r="BX4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BY4" t="n">
         <v>0</v>
       </c>
       <c r="BZ4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CA4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CB4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CC4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CD4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CE4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CG4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CH4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CI4" t="n">
         <v>0</v>
@@ -2291,10 +2291,10 @@
         <v>1</v>
       </c>
       <c r="CK4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CL4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CM4" t="n">
         <v>0</v>
@@ -2306,16 +2306,16 @@
         <v>0</v>
       </c>
       <c r="CP4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CQ4" t="n">
         <v>2</v>
       </c>
       <c r="CR4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CS4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CT4" t="n">
         <v>3</v>
@@ -2327,31 +2327,31 @@
         <v>1</v>
       </c>
       <c r="CW4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CX4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="CY4" t="n">
         <v>0</v>
       </c>
       <c r="CZ4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DA4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="DB4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DC4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DD4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="DE4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DF4" t="n">
         <v>3</v>
@@ -2360,7 +2360,7 @@
         <v>0</v>
       </c>
       <c r="DH4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="DI4" t="n">
         <v>0</v>
@@ -2369,28 +2369,28 @@
         <v>2</v>
       </c>
       <c r="DK4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DL4" t="n">
         <v>0</v>
       </c>
       <c r="DM4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DN4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DO4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DP4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DQ4" t="n">
         <v>4</v>
       </c>
       <c r="DR4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DS4" t="n">
         <v>0</v>
@@ -2399,46 +2399,46 @@
         <v>0</v>
       </c>
       <c r="DU4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="DV4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="DW4" t="n">
         <v>0</v>
       </c>
       <c r="DX4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="DY4" t="n">
         <v>0</v>
       </c>
       <c r="DZ4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="EA4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="EB4" t="n">
         <v>0</v>
       </c>
       <c r="EC4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="ED4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="EE4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="EF4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EG4" t="n">
         <v>0</v>
       </c>
       <c r="EH4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="EI4" t="n">
         <v>0</v>
@@ -2447,101 +2447,101 @@
         <v>0</v>
       </c>
       <c r="EK4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="EL4" t="n">
         <v>1</v>
       </c>
       <c r="EM4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="EN4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="EO4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Marcio</t>
+          <t>Gustavo Marini</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
         <v>2</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
         <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R5" t="n">
         <v>2</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA5" t="n">
         <v>1</v>
@@ -2553,112 +2553,112 @@
         <v>2</v>
       </c>
       <c r="AD5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE5" t="n">
         <v>2</v>
       </c>
       <c r="AF5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG5" t="n">
         <v>4</v>
       </c>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>3</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>5</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>2</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>2</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>3</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>1</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>2</v>
-      </c>
       <c r="BH5" t="n">
         <v>0</v>
       </c>
       <c r="BI5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BJ5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BK5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BL5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BM5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BN5" t="n">
         <v>2</v>
@@ -2670,7 +2670,7 @@
         <v>0</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BR5" t="n">
         <v>1</v>
@@ -2679,46 +2679,46 @@
         <v>1</v>
       </c>
       <c r="BT5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU5" t="n">
         <v>3</v>
       </c>
       <c r="BV5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BX5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BY5" t="n">
         <v>0</v>
       </c>
       <c r="BZ5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CA5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CB5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CC5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CD5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CE5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CG5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CH5" t="n">
         <v>4</v>
@@ -2727,34 +2727,34 @@
         <v>0</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CK5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CL5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CM5" t="n">
         <v>0</v>
       </c>
       <c r="CN5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CO5" t="n">
         <v>0</v>
       </c>
       <c r="CP5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CQ5" t="n">
         <v>2</v>
       </c>
       <c r="CR5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CS5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CT5" t="n">
         <v>3</v>
@@ -2763,7 +2763,7 @@
         <v>1</v>
       </c>
       <c r="CV5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CW5" t="n">
         <v>2</v>
@@ -2775,31 +2775,31 @@
         <v>0</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="DA5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DB5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DC5" t="n">
         <v>2</v>
       </c>
       <c r="DD5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="DE5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="DF5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DG5" t="n">
         <v>0</v>
       </c>
       <c r="DH5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="DI5" t="n">
         <v>0</v>
@@ -2814,22 +2814,22 @@
         <v>0</v>
       </c>
       <c r="DM5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DN5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DP5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DQ5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DR5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="DS5" t="n">
         <v>0</v>
@@ -2838,40 +2838,40 @@
         <v>0</v>
       </c>
       <c r="DU5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DW5" t="n">
         <v>0</v>
       </c>
       <c r="DX5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="DY5" t="n">
         <v>0</v>
       </c>
       <c r="DZ5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="EA5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="EB5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EC5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="ED5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="EE5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="EF5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="EG5" t="n">
         <v>0</v>
@@ -2880,22 +2880,22 @@
         <v>2</v>
       </c>
       <c r="EI5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EJ5" t="n">
         <v>0</v>
       </c>
       <c r="EK5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="EL5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EM5" t="n">
         <v>2</v>
       </c>
       <c r="EN5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="EO5" t="n">
         <v>1</v>
@@ -2904,14 +2904,14 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Pedro Thedim</t>
+          <t>Marcio</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
@@ -2926,28 +2926,28 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
         <v>1</v>
       </c>
       <c r="N6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -2962,16 +2962,16 @@
         <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U6" t="n">
         <v>1</v>
       </c>
       <c r="V6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>1</v>
@@ -2980,7 +2980,7 @@
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA6" t="n">
         <v>1</v>
@@ -2992,176 +2992,176 @@
         <v>2</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX6" t="n">
         <v>5</v>
       </c>
-      <c r="AG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>3</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>6</v>
-      </c>
       <c r="AY6" t="n">
         <v>0</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BA6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB6" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>3</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>2</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>2</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>2</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>1</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>3</v>
+      </c>
+      <c r="CH6" t="n">
         <v>4</v>
       </c>
-      <c r="BC6" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>2</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>1</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>1</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>2</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>2</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>1</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>1</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>3</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>2</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>1</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>1</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>2</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>1</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>1</v>
-      </c>
-      <c r="BX6" t="n">
-        <v>2</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ6" t="n">
-        <v>1</v>
-      </c>
-      <c r="CA6" t="n">
-        <v>1</v>
-      </c>
-      <c r="CB6" t="n">
-        <v>1</v>
-      </c>
-      <c r="CC6" t="n">
-        <v>2</v>
-      </c>
-      <c r="CD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG6" t="n">
-        <v>3</v>
-      </c>
-      <c r="CH6" t="n">
-        <v>6</v>
-      </c>
       <c r="CI6" t="n">
         <v>0</v>
       </c>
@@ -3172,10 +3172,10 @@
         <v>2</v>
       </c>
       <c r="CL6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CM6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN6" t="n">
         <v>3</v>
@@ -3184,16 +3184,16 @@
         <v>0</v>
       </c>
       <c r="CP6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CR6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CS6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CT6" t="n">
         <v>3</v>
@@ -3205,10 +3205,10 @@
         <v>0</v>
       </c>
       <c r="CW6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CX6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="CY6" t="n">
         <v>0</v>
@@ -3220,16 +3220,16 @@
         <v>1</v>
       </c>
       <c r="DB6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="DC6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="DD6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="DE6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DF6" t="n">
         <v>2</v>
@@ -3241,22 +3241,22 @@
         <v>2</v>
       </c>
       <c r="DI6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="DJ6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DK6" t="n">
         <v>0</v>
       </c>
       <c r="DL6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DM6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="DN6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DO6" t="n">
         <v>1</v>
@@ -3268,10 +3268,10 @@
         <v>3</v>
       </c>
       <c r="DR6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="DS6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT6" t="n">
         <v>0</v>
@@ -3280,7 +3280,7 @@
         <v>2</v>
       </c>
       <c r="DV6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DW6" t="n">
         <v>0</v>
@@ -3292,7 +3292,7 @@
         <v>0</v>
       </c>
       <c r="DZ6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="EA6" t="n">
         <v>2</v>
@@ -3304,7 +3304,7 @@
         <v>1</v>
       </c>
       <c r="ED6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="EE6" t="n">
         <v>1</v>
@@ -3313,13 +3313,13 @@
         <v>2</v>
       </c>
       <c r="EG6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="EH6" t="n">
         <v>2</v>
       </c>
       <c r="EI6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EJ6" t="n">
         <v>0</v>
@@ -3331,41 +3331,41 @@
         <v>0</v>
       </c>
       <c r="EM6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="EN6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="EO6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Rafael Souto</t>
+          <t>Pedro Thedim</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
@@ -3374,7 +3374,7 @@
         <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -3383,163 +3383,163 @@
         <v>1</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
+        <v>2</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB7" t="n">
         <v>4</v>
       </c>
-      <c r="R7" t="n">
-        <v>2</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1</v>
-      </c>
-      <c r="W7" t="n">
-        <v>2</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>6</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>4</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>3</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>5</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>1</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>3</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>3</v>
-      </c>
       <c r="BC7" t="n">
         <v>1</v>
       </c>
       <c r="BD7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BE7" t="n">
         <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BG7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BH7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BI7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BJ7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BK7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BL7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BM7" t="n">
         <v>1</v>
       </c>
       <c r="BN7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BO7" t="n">
         <v>0</v>
@@ -3548,37 +3548,37 @@
         <v>0</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BR7" t="n">
         <v>2</v>
       </c>
       <c r="BS7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BT7" t="n">
         <v>1</v>
       </c>
       <c r="BU7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BV7" t="n">
         <v>1</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BX7" t="n">
         <v>2</v>
       </c>
       <c r="BY7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BZ7" t="n">
         <v>1</v>
       </c>
       <c r="CA7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CB7" t="n">
         <v>1</v>
@@ -3590,13 +3590,13 @@
         <v>0</v>
       </c>
       <c r="CE7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CF7" t="n">
         <v>0</v>
       </c>
       <c r="CG7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CH7" t="n">
         <v>6</v>
@@ -3608,109 +3608,109 @@
         <v>0</v>
       </c>
       <c r="CK7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CL7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CM7" t="n">
         <v>1</v>
       </c>
       <c r="CN7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CO7" t="n">
         <v>0</v>
       </c>
       <c r="CP7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CQ7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CR7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CS7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="CT7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="CU7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CV7" t="n">
         <v>0</v>
       </c>
       <c r="CW7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CX7" t="n">
         <v>5</v>
       </c>
       <c r="CY7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CZ7" t="n">
         <v>2</v>
       </c>
       <c r="DA7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="DB7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DC7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DD7" t="n">
+        <v>2</v>
+      </c>
+      <c r="DE7" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF7" t="n">
+        <v>2</v>
+      </c>
+      <c r="DG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH7" t="n">
+        <v>2</v>
+      </c>
+      <c r="DI7" t="n">
+        <v>2</v>
+      </c>
+      <c r="DJ7" t="n">
+        <v>1</v>
+      </c>
+      <c r="DK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL7" t="n">
+        <v>1</v>
+      </c>
+      <c r="DM7" t="n">
+        <v>2</v>
+      </c>
+      <c r="DN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO7" t="n">
+        <v>1</v>
+      </c>
+      <c r="DP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ7" t="n">
+        <v>3</v>
+      </c>
+      <c r="DR7" t="n">
         <v>4</v>
       </c>
-      <c r="DE7" t="n">
-        <v>2</v>
-      </c>
-      <c r="DF7" t="n">
-        <v>2</v>
-      </c>
-      <c r="DG7" t="n">
-        <v>1</v>
-      </c>
-      <c r="DH7" t="n">
-        <v>4</v>
-      </c>
-      <c r="DI7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ7" t="n">
-        <v>1</v>
-      </c>
-      <c r="DK7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DM7" t="n">
-        <v>1</v>
-      </c>
-      <c r="DN7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DO7" t="n">
-        <v>1</v>
-      </c>
-      <c r="DP7" t="n">
-        <v>2</v>
-      </c>
-      <c r="DQ7" t="n">
-        <v>6</v>
-      </c>
-      <c r="DR7" t="n">
-        <v>7</v>
-      </c>
       <c r="DS7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT7" t="n">
         <v>0</v>
@@ -3719,40 +3719,40 @@
         <v>2</v>
       </c>
       <c r="DV7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="DW7" t="n">
         <v>0</v>
       </c>
       <c r="DX7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="DY7" t="n">
         <v>0</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EA7" t="n">
         <v>2</v>
       </c>
       <c r="EB7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EC7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="ED7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="EE7" t="n">
         <v>1</v>
       </c>
       <c r="EF7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="EG7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="EH7" t="n">
         <v>2</v>
@@ -3767,59 +3767,59 @@
         <v>2</v>
       </c>
       <c r="EL7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EM7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="EN7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="EO7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Victor Bethlem</t>
+          <t>Rafael Souto</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
         <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I8" t="n">
         <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N8" t="n">
         <v>1</v>
@@ -3828,31 +3828,31 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
@@ -3864,74 +3864,74 @@
         <v>1</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AF8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX8" t="n">
         <v>5</v>
       </c>
-      <c r="AG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>3</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>3</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>3</v>
-      </c>
       <c r="AY8" t="n">
         <v>0</v>
       </c>
@@ -3939,34 +3939,34 @@
         <v>1</v>
       </c>
       <c r="BA8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BB8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BC8" t="n">
         <v>1</v>
       </c>
       <c r="BD8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BE8" t="n">
         <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BG8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BH8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BI8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BJ8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BK8" t="n">
         <v>2</v>
@@ -3975,7 +3975,7 @@
         <v>1</v>
       </c>
       <c r="BM8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BN8" t="n">
         <v>2</v>
@@ -3993,7 +3993,7 @@
         <v>2</v>
       </c>
       <c r="BS8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BT8" t="n">
         <v>1</v>
@@ -4005,28 +4005,28 @@
         <v>1</v>
       </c>
       <c r="BW8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BX8" t="n">
         <v>2</v>
       </c>
       <c r="BY8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CA8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CB8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CC8" t="n">
         <v>2</v>
       </c>
       <c r="CD8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE8" t="n">
         <v>2</v>
@@ -4038,157 +4038,157 @@
         <v>4</v>
       </c>
       <c r="CH8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="CI8" t="n">
         <v>0</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CK8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CL8" t="n">
         <v>3</v>
       </c>
       <c r="CM8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CO8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CP8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CR8" t="n">
         <v>1</v>
       </c>
       <c r="CS8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="CT8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CU8" t="n">
         <v>0</v>
       </c>
       <c r="CV8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CW8" t="n">
+        <v>2</v>
+      </c>
+      <c r="CX8" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY8" t="n">
+        <v>1</v>
+      </c>
+      <c r="CZ8" t="n">
+        <v>2</v>
+      </c>
+      <c r="DA8" t="n">
+        <v>2</v>
+      </c>
+      <c r="DB8" t="n">
+        <v>1</v>
+      </c>
+      <c r="DC8" t="n">
+        <v>2</v>
+      </c>
+      <c r="DD8" t="n">
         <v>4</v>
       </c>
-      <c r="CX8" t="n">
-        <v>2</v>
-      </c>
-      <c r="CY8" t="n">
-        <v>0</v>
-      </c>
-      <c r="CZ8" t="n">
-        <v>1</v>
-      </c>
-      <c r="DA8" t="n">
-        <v>1</v>
-      </c>
-      <c r="DB8" t="n">
-        <v>1</v>
-      </c>
-      <c r="DC8" t="n">
-        <v>1</v>
-      </c>
-      <c r="DD8" t="n">
-        <v>3</v>
-      </c>
       <c r="DE8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DF8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DG8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DH8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="DK8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DL8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DM8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="DN8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="DP8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="DQ8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="DR8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="DS8" t="n">
         <v>0</v>
       </c>
       <c r="DT8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU8" t="n">
         <v>2</v>
       </c>
       <c r="DV8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DW8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DX8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="DY8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="DZ8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EA8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="EB8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EC8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="ED8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="EE8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EF8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="EG8" t="n">
         <v>1</v>
@@ -4200,21 +4200,460 @@
         <v>0</v>
       </c>
       <c r="EJ8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EK8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="EL8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EM8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="EN8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="EO8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Victor Bethlem</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>3</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>2</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>2</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>1</v>
+      </c>
+      <c r="CB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC9" t="n">
+        <v>2</v>
+      </c>
+      <c r="CD9" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE9" t="n">
+        <v>2</v>
+      </c>
+      <c r="CF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG9" t="n">
+        <v>4</v>
+      </c>
+      <c r="CH9" t="n">
+        <v>3</v>
+      </c>
+      <c r="CI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ9" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK9" t="n">
+        <v>2</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>3</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN9" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO9" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP9" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR9" t="n">
+        <v>1</v>
+      </c>
+      <c r="CS9" t="n">
+        <v>2</v>
+      </c>
+      <c r="CT9" t="n">
+        <v>3</v>
+      </c>
+      <c r="CU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV9" t="n">
+        <v>1</v>
+      </c>
+      <c r="CW9" t="n">
+        <v>4</v>
+      </c>
+      <c r="CX9" t="n">
+        <v>2</v>
+      </c>
+      <c r="CY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ9" t="n">
+        <v>1</v>
+      </c>
+      <c r="DA9" t="n">
+        <v>1</v>
+      </c>
+      <c r="DB9" t="n">
+        <v>1</v>
+      </c>
+      <c r="DC9" t="n">
+        <v>1</v>
+      </c>
+      <c r="DD9" t="n">
+        <v>3</v>
+      </c>
+      <c r="DE9" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF9" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH9" t="n">
+        <v>2</v>
+      </c>
+      <c r="DI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ9" t="n">
+        <v>2</v>
+      </c>
+      <c r="DK9" t="n">
+        <v>1</v>
+      </c>
+      <c r="DL9" t="n">
+        <v>1</v>
+      </c>
+      <c r="DM9" t="n">
+        <v>3</v>
+      </c>
+      <c r="DN9" t="n">
+        <v>1</v>
+      </c>
+      <c r="DO9" t="n">
+        <v>2</v>
+      </c>
+      <c r="DP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ9" t="n">
+        <v>3</v>
+      </c>
+      <c r="DR9" t="n">
+        <v>1</v>
+      </c>
+      <c r="DS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT9" t="n">
+        <v>1</v>
+      </c>
+      <c r="DU9" t="n">
+        <v>2</v>
+      </c>
+      <c r="DV9" t="n">
+        <v>3</v>
+      </c>
+      <c r="DW9" t="n">
+        <v>1</v>
+      </c>
+      <c r="DX9" t="n">
+        <v>2</v>
+      </c>
+      <c r="DY9" t="n">
+        <v>2</v>
+      </c>
+      <c r="DZ9" t="n">
+        <v>1</v>
+      </c>
+      <c r="EA9" t="n">
+        <v>1</v>
+      </c>
+      <c r="EB9" t="n">
+        <v>1</v>
+      </c>
+      <c r="EC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED9" t="n">
+        <v>2</v>
+      </c>
+      <c r="EE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF9" t="n">
+        <v>1</v>
+      </c>
+      <c r="EG9" t="n">
+        <v>1</v>
+      </c>
+      <c r="EH9" t="n">
+        <v>2</v>
+      </c>
+      <c r="EI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ9" t="n">
+        <v>1</v>
+      </c>
+      <c r="EK9" t="n">
+        <v>1</v>
+      </c>
+      <c r="EL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM9" t="n">
+        <v>2</v>
+      </c>
+      <c r="EN9" t="n">
+        <v>1</v>
+      </c>
+      <c r="EO9" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4229,7 +4668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM8"/>
+  <dimension ref="A1:BM9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4896,10 +5335,10 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Gustavo Marini</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
+          <t>Ana Leticia Xavier</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -4924,12 +5363,12 @@
           <t>X</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -4949,7 +5388,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -4974,12 +5413,12 @@
           <t>X</t>
         </is>
       </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -5029,7 +5468,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="BB4" t="inlineStr">
+      <c r="BC4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -5039,7 +5478,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr">
+      <c r="BF4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -5054,7 +5493,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="BM4" t="inlineStr">
+      <c r="BL4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -5063,10 +5502,10 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Marcio</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
+          <t>Gustavo Marini</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -5076,7 +5515,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -5091,12 +5530,12 @@
           <t>X</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -5116,7 +5555,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -5141,12 +5580,12 @@
           <t>X</t>
         </is>
       </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -5171,7 +5610,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="AS5" t="inlineStr">
+      <c r="AR5" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -5211,7 +5650,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="BI5" t="inlineStr">
+      <c r="BH5" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -5221,7 +5660,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="BL5" t="inlineStr">
+      <c r="BM5" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -5230,10 +5669,10 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Pedro Thedim</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
+          <t>Marcio</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -5298,7 +5737,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -5308,171 +5747,171 @@
           <t>X</t>
         </is>
       </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>x</t>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>x</t>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="BK6" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="BM6" t="inlineStr">
-        <is>
-          <t>x</t>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Rafael Souto</t>
+          <t>Pedro Thedim</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>x</t>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>x</t>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
@@ -5530,7 +5969,7 @@
           <t>x</t>
         </is>
       </c>
-      <c r="BC7" t="inlineStr">
+      <c r="BB7" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -5545,17 +5984,17 @@
           <t>x</t>
         </is>
       </c>
-      <c r="BI7" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="BJ7" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="BL7" t="inlineStr">
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -5564,165 +6003,332 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>Rafael Souto</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>Victor Bethlem</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="BE8" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="BI8" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="BJ8" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="BM8" t="inlineStr">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="BM9" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -5739,7 +6345,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5796,83 +6402,100 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Gustavo Marini</t>
+          <t>Ana Leticia Xavier</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Danilo</t>
+          <t>Kylian Mbappé</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Espanha</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Marcio</t>
+          <t>Gustavo Marini</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Harry Kane</t>
+          <t>Danilo Santos</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>Brasil</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Pedro Thedim</t>
+          <t>Marcio</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kylian Mbappé</t>
+          <t>Harry Kane</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Franca</t>
+          <t>Espanha</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Rafael Souto</t>
+          <t>Pedro Thedim</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Julián Álvarez</t>
+          <t>Kylian Mbappé</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Franca</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>Rafael Souto</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Julián Álvarez</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>Victor Bethlem</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Kylian Mbappé</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Inglaterra</t>
         </is>

--- a/apostas/Bolao_Copa2026_TurimMFO - Consolidada.xlsx
+++ b/apostas/Bolao_Copa2026_TurimMFO - Consolidada.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EO9"/>
+  <dimension ref="A1:EO10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2026,35 +2026,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ana Leticia Xavier</t>
+          <t>Rafaela Albano Ribeiro</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
         <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
         <v>1</v>
@@ -2063,40 +2063,40 @@
         <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
@@ -2108,7 +2108,7 @@
         <v>1</v>
       </c>
       <c r="AB4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
         <v>3</v>
@@ -2117,19 +2117,19 @@
         <v>1</v>
       </c>
       <c r="AE4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AJ4" t="n">
         <v>3</v>
@@ -2138,7 +2138,7 @@
         <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AM4" t="n">
         <v>0</v>
@@ -2147,7 +2147,7 @@
         <v>1</v>
       </c>
       <c r="AO4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AP4" t="n">
         <v>1</v>
@@ -2165,7 +2165,7 @@
         <v>1</v>
       </c>
       <c r="AU4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV4" t="n">
         <v>0</v>
@@ -2180,31 +2180,31 @@
         <v>0</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA4" t="n">
         <v>1</v>
       </c>
       <c r="BB4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BC4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF4" t="n">
         <v>1</v>
       </c>
       <c r="BG4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BH4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BI4" t="n">
         <v>2</v>
@@ -2213,7 +2213,7 @@
         <v>2</v>
       </c>
       <c r="BK4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BL4" t="n">
         <v>1</v>
@@ -2222,16 +2222,16 @@
         <v>0</v>
       </c>
       <c r="BN4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BO4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BP4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BR4" t="n">
         <v>1</v>
@@ -2243,10 +2243,10 @@
         <v>0</v>
       </c>
       <c r="BU4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BV4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BW4" t="n">
         <v>1</v>
@@ -2267,13 +2267,13 @@
         <v>0</v>
       </c>
       <c r="CC4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CD4" t="n">
         <v>1</v>
       </c>
       <c r="CE4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF4" t="n">
         <v>0</v>
@@ -2291,16 +2291,16 @@
         <v>1</v>
       </c>
       <c r="CK4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CL4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CM4" t="n">
         <v>0</v>
       </c>
       <c r="CN4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CO4" t="n">
         <v>0</v>
@@ -2309,28 +2309,28 @@
         <v>1</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CR4" t="n">
         <v>1</v>
       </c>
       <c r="CS4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CT4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CU4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CV4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CW4" t="n">
         <v>3</v>
       </c>
       <c r="CX4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CY4" t="n">
         <v>0</v>
@@ -2345,7 +2345,7 @@
         <v>1</v>
       </c>
       <c r="DC4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="DD4" t="n">
         <v>2</v>
@@ -2354,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="DG4" t="n">
         <v>0</v>
       </c>
       <c r="DH4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="DI4" t="n">
         <v>0</v>
@@ -2372,13 +2372,13 @@
         <v>1</v>
       </c>
       <c r="DL4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DM4" t="n">
         <v>1</v>
       </c>
       <c r="DN4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DO4" t="n">
         <v>1</v>
@@ -2387,7 +2387,7 @@
         <v>0</v>
       </c>
       <c r="DQ4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="DR4" t="n">
         <v>3</v>
@@ -2408,55 +2408,55 @@
         <v>0</v>
       </c>
       <c r="DX4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="DY4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DZ4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="EA4" t="n">
         <v>2</v>
       </c>
       <c r="EB4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EC4" t="n">
         <v>1</v>
       </c>
       <c r="ED4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="EE4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EF4" t="n">
         <v>1</v>
       </c>
       <c r="EG4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="EH4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="EI4" t="n">
         <v>0</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EK4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="EL4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EM4" t="n">
         <v>4</v>
       </c>
       <c r="EN4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="EO4" t="n">
         <v>0</v>
@@ -2465,20 +2465,20 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Gustavo Marini</t>
+          <t>Ana Leticia Xavier</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
         <v>2</v>
@@ -2490,28 +2490,28 @@
         <v>2</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K5" t="n">
         <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
       </c>
       <c r="P5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>3</v>
@@ -2523,70 +2523,70 @@
         <v>2</v>
       </c>
       <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" t="n">
+        <v>2</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF5" t="n">
         <v>4</v>
       </c>
-      <c r="U5" t="n">
-        <v>2</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1</v>
-      </c>
-      <c r="X5" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>6</v>
-      </c>
       <c r="AG5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ5" t="n">
         <v>3</v>
       </c>
       <c r="AK5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM5" t="n">
         <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AP5" t="n">
         <v>1</v>
@@ -2604,25 +2604,25 @@
         <v>1</v>
       </c>
       <c r="AU5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AX5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AY5" t="n">
         <v>0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB5" t="n">
         <v>3</v>
@@ -2634,40 +2634,40 @@
         <v>2</v>
       </c>
       <c r="BE5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BG5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BH5" t="n">
         <v>0</v>
       </c>
       <c r="BI5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BJ5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BK5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BL5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BM5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BN5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BO5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BP5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ5" t="n">
         <v>2</v>
@@ -2679,49 +2679,49 @@
         <v>1</v>
       </c>
       <c r="BT5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BV5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BW5" t="n">
         <v>1</v>
       </c>
       <c r="BX5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BY5" t="n">
         <v>0</v>
       </c>
       <c r="BZ5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CB5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CC5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CD5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CE5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CG5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CH5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CI5" t="n">
         <v>0</v>
@@ -2730,10 +2730,10 @@
         <v>1</v>
       </c>
       <c r="CK5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CL5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CM5" t="n">
         <v>0</v>
@@ -2745,16 +2745,16 @@
         <v>0</v>
       </c>
       <c r="CP5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CQ5" t="n">
         <v>2</v>
       </c>
       <c r="CR5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CS5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CT5" t="n">
         <v>3</v>
@@ -2766,31 +2766,31 @@
         <v>1</v>
       </c>
       <c r="CW5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CX5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="CY5" t="n">
         <v>0</v>
       </c>
       <c r="CZ5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DA5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="DB5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DC5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DD5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="DE5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DF5" t="n">
         <v>3</v>
@@ -2799,7 +2799,7 @@
         <v>0</v>
       </c>
       <c r="DH5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="DI5" t="n">
         <v>0</v>
@@ -2808,28 +2808,28 @@
         <v>2</v>
       </c>
       <c r="DK5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DL5" t="n">
         <v>0</v>
       </c>
       <c r="DM5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DN5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DO5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DP5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DQ5" t="n">
         <v>4</v>
       </c>
       <c r="DR5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DS5" t="n">
         <v>0</v>
@@ -2838,46 +2838,46 @@
         <v>0</v>
       </c>
       <c r="DU5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="DV5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="DW5" t="n">
         <v>0</v>
       </c>
       <c r="DX5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="DY5" t="n">
         <v>0</v>
       </c>
       <c r="DZ5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="EA5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="EB5" t="n">
         <v>0</v>
       </c>
       <c r="EC5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="ED5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="EE5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="EF5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EG5" t="n">
         <v>0</v>
       </c>
       <c r="EH5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="EI5" t="n">
         <v>0</v>
@@ -2886,101 +2886,101 @@
         <v>0</v>
       </c>
       <c r="EK5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="EL5" t="n">
         <v>1</v>
       </c>
       <c r="EM5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="EN5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="EO5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Marcio</t>
+          <t>Gustavo Marini</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
         <v>2</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R6" t="n">
         <v>2</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA6" t="n">
         <v>1</v>
@@ -2992,112 +2992,112 @@
         <v>2</v>
       </c>
       <c r="AD6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE6" t="n">
         <v>2</v>
       </c>
       <c r="AF6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG6" t="n">
         <v>4</v>
       </c>
-      <c r="AG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>3</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>5</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>2</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>2</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>3</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>1</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>2</v>
-      </c>
       <c r="BH6" t="n">
         <v>0</v>
       </c>
       <c r="BI6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BJ6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BK6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BL6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BM6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BN6" t="n">
         <v>2</v>
@@ -3109,7 +3109,7 @@
         <v>0</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BR6" t="n">
         <v>1</v>
@@ -3118,46 +3118,46 @@
         <v>1</v>
       </c>
       <c r="BT6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU6" t="n">
         <v>3</v>
       </c>
       <c r="BV6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BW6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BX6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BY6" t="n">
         <v>0</v>
       </c>
       <c r="BZ6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CA6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CB6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CC6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CD6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CE6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CG6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CH6" t="n">
         <v>4</v>
@@ -3166,34 +3166,34 @@
         <v>0</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CK6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CL6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CM6" t="n">
         <v>0</v>
       </c>
       <c r="CN6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CO6" t="n">
         <v>0</v>
       </c>
       <c r="CP6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CQ6" t="n">
         <v>2</v>
       </c>
       <c r="CR6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CS6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CT6" t="n">
         <v>3</v>
@@ -3202,7 +3202,7 @@
         <v>1</v>
       </c>
       <c r="CV6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CW6" t="n">
         <v>2</v>
@@ -3214,31 +3214,31 @@
         <v>0</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="DA6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DB6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DC6" t="n">
         <v>2</v>
       </c>
       <c r="DD6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="DE6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="DF6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DG6" t="n">
         <v>0</v>
       </c>
       <c r="DH6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="DI6" t="n">
         <v>0</v>
@@ -3253,22 +3253,22 @@
         <v>0</v>
       </c>
       <c r="DM6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DN6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DP6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DQ6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DR6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="DS6" t="n">
         <v>0</v>
@@ -3277,40 +3277,40 @@
         <v>0</v>
       </c>
       <c r="DU6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DW6" t="n">
         <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="DY6" t="n">
         <v>0</v>
       </c>
       <c r="DZ6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="EA6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="EB6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EC6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="ED6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="EE6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="EF6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="EG6" t="n">
         <v>0</v>
@@ -3319,22 +3319,22 @@
         <v>2</v>
       </c>
       <c r="EI6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EJ6" t="n">
         <v>0</v>
       </c>
       <c r="EK6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="EL6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EM6" t="n">
         <v>2</v>
       </c>
       <c r="EN6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="EO6" t="n">
         <v>1</v>
@@ -3343,14 +3343,14 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Pedro Thedim</t>
+          <t>Marcio</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
@@ -3365,28 +3365,28 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
         <v>1</v>
       </c>
       <c r="N7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -3401,16 +3401,16 @@
         <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U7" t="n">
         <v>1</v>
       </c>
       <c r="V7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>1</v>
@@ -3419,7 +3419,7 @@
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA7" t="n">
         <v>1</v>
@@ -3431,176 +3431,176 @@
         <v>2</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="n">
         <v>5</v>
       </c>
-      <c r="AG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>3</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>6</v>
-      </c>
       <c r="AY7" t="n">
         <v>0</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BA7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>3</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>2</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>1</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>3</v>
+      </c>
+      <c r="CH7" t="n">
         <v>4</v>
       </c>
-      <c r="BC7" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>2</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>1</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>1</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>2</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>2</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>1</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>1</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>3</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>2</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>1</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>1</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>2</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>1</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>1</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>2</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ7" t="n">
-        <v>1</v>
-      </c>
-      <c r="CA7" t="n">
-        <v>1</v>
-      </c>
-      <c r="CB7" t="n">
-        <v>1</v>
-      </c>
-      <c r="CC7" t="n">
-        <v>2</v>
-      </c>
-      <c r="CD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG7" t="n">
-        <v>3</v>
-      </c>
-      <c r="CH7" t="n">
-        <v>6</v>
-      </c>
       <c r="CI7" t="n">
         <v>0</v>
       </c>
@@ -3611,10 +3611,10 @@
         <v>2</v>
       </c>
       <c r="CL7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CM7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN7" t="n">
         <v>3</v>
@@ -3623,16 +3623,16 @@
         <v>0</v>
       </c>
       <c r="CP7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CR7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CS7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CT7" t="n">
         <v>3</v>
@@ -3644,10 +3644,10 @@
         <v>0</v>
       </c>
       <c r="CW7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CX7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="CY7" t="n">
         <v>0</v>
@@ -3659,16 +3659,16 @@
         <v>1</v>
       </c>
       <c r="DB7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="DC7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="DD7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="DE7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DF7" t="n">
         <v>2</v>
@@ -3680,22 +3680,22 @@
         <v>2</v>
       </c>
       <c r="DI7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DK7" t="n">
         <v>0</v>
       </c>
       <c r="DL7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DM7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="DN7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DO7" t="n">
         <v>1</v>
@@ -3707,10 +3707,10 @@
         <v>3</v>
       </c>
       <c r="DR7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="DS7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT7" t="n">
         <v>0</v>
@@ -3719,7 +3719,7 @@
         <v>2</v>
       </c>
       <c r="DV7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DW7" t="n">
         <v>0</v>
@@ -3731,7 +3731,7 @@
         <v>0</v>
       </c>
       <c r="DZ7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="EA7" t="n">
         <v>2</v>
@@ -3743,7 +3743,7 @@
         <v>1</v>
       </c>
       <c r="ED7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="EE7" t="n">
         <v>1</v>
@@ -3752,13 +3752,13 @@
         <v>2</v>
       </c>
       <c r="EG7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="EH7" t="n">
         <v>2</v>
       </c>
       <c r="EI7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EJ7" t="n">
         <v>0</v>
@@ -3770,41 +3770,41 @@
         <v>0</v>
       </c>
       <c r="EM7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="EN7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="EO7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Rafael Souto</t>
+          <t>Pedro Thedim</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
         <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>1</v>
@@ -3813,7 +3813,7 @@
         <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -3822,163 +3822,163 @@
         <v>1</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
+        <v>2</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB8" t="n">
         <v>4</v>
       </c>
-      <c r="R8" t="n">
-        <v>2</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1</v>
-      </c>
-      <c r="W8" t="n">
-        <v>2</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>6</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>4</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>3</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>5</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>1</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>3</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>3</v>
-      </c>
       <c r="BC8" t="n">
         <v>1</v>
       </c>
       <c r="BD8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BE8" t="n">
         <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BG8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BH8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BI8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BJ8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BK8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BL8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BM8" t="n">
         <v>1</v>
       </c>
       <c r="BN8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BO8" t="n">
         <v>0</v>
@@ -3987,37 +3987,37 @@
         <v>0</v>
       </c>
       <c r="BQ8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BR8" t="n">
         <v>2</v>
       </c>
       <c r="BS8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BT8" t="n">
         <v>1</v>
       </c>
       <c r="BU8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BV8" t="n">
         <v>1</v>
       </c>
       <c r="BW8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BX8" t="n">
         <v>2</v>
       </c>
       <c r="BY8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BZ8" t="n">
         <v>1</v>
       </c>
       <c r="CA8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CB8" t="n">
         <v>1</v>
@@ -4029,13 +4029,13 @@
         <v>0</v>
       </c>
       <c r="CE8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CF8" t="n">
         <v>0</v>
       </c>
       <c r="CG8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CH8" t="n">
         <v>6</v>
@@ -4047,109 +4047,109 @@
         <v>0</v>
       </c>
       <c r="CK8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CL8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CM8" t="n">
         <v>1</v>
       </c>
       <c r="CN8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CO8" t="n">
         <v>0</v>
       </c>
       <c r="CP8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CR8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CS8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="CT8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="CU8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CV8" t="n">
         <v>0</v>
       </c>
       <c r="CW8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CX8" t="n">
         <v>5</v>
       </c>
       <c r="CY8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CZ8" t="n">
         <v>2</v>
       </c>
       <c r="DA8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="DB8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DC8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DD8" t="n">
+        <v>2</v>
+      </c>
+      <c r="DE8" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF8" t="n">
+        <v>2</v>
+      </c>
+      <c r="DG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH8" t="n">
+        <v>2</v>
+      </c>
+      <c r="DI8" t="n">
+        <v>2</v>
+      </c>
+      <c r="DJ8" t="n">
+        <v>1</v>
+      </c>
+      <c r="DK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL8" t="n">
+        <v>1</v>
+      </c>
+      <c r="DM8" t="n">
+        <v>2</v>
+      </c>
+      <c r="DN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO8" t="n">
+        <v>1</v>
+      </c>
+      <c r="DP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ8" t="n">
+        <v>3</v>
+      </c>
+      <c r="DR8" t="n">
         <v>4</v>
       </c>
-      <c r="DE8" t="n">
-        <v>2</v>
-      </c>
-      <c r="DF8" t="n">
-        <v>2</v>
-      </c>
-      <c r="DG8" t="n">
-        <v>1</v>
-      </c>
-      <c r="DH8" t="n">
-        <v>4</v>
-      </c>
-      <c r="DI8" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ8" t="n">
-        <v>1</v>
-      </c>
-      <c r="DK8" t="n">
-        <v>0</v>
-      </c>
-      <c r="DL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="DM8" t="n">
-        <v>1</v>
-      </c>
-      <c r="DN8" t="n">
-        <v>0</v>
-      </c>
-      <c r="DO8" t="n">
-        <v>1</v>
-      </c>
-      <c r="DP8" t="n">
-        <v>2</v>
-      </c>
-      <c r="DQ8" t="n">
-        <v>6</v>
-      </c>
-      <c r="DR8" t="n">
-        <v>7</v>
-      </c>
       <c r="DS8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT8" t="n">
         <v>0</v>
@@ -4158,40 +4158,40 @@
         <v>2</v>
       </c>
       <c r="DV8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="DW8" t="n">
         <v>0</v>
       </c>
       <c r="DX8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="DY8" t="n">
         <v>0</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EA8" t="n">
         <v>2</v>
       </c>
       <c r="EB8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EC8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="ED8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="EE8" t="n">
         <v>1</v>
       </c>
       <c r="EF8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="EG8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="EH8" t="n">
         <v>2</v>
@@ -4206,59 +4206,59 @@
         <v>2</v>
       </c>
       <c r="EL8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EM8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="EN8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="EO8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Victor Bethlem</t>
+          <t>Rafael Souto</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N9" t="n">
         <v>1</v>
@@ -4267,31 +4267,31 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
@@ -4303,74 +4303,74 @@
         <v>1</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AF9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX9" t="n">
         <v>5</v>
       </c>
-      <c r="AG9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>3</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>3</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>3</v>
-      </c>
       <c r="AY9" t="n">
         <v>0</v>
       </c>
@@ -4378,34 +4378,34 @@
         <v>1</v>
       </c>
       <c r="BA9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BB9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BC9" t="n">
         <v>1</v>
       </c>
       <c r="BD9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BE9" t="n">
         <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BG9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BH9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BI9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BJ9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BK9" t="n">
         <v>2</v>
@@ -4414,7 +4414,7 @@
         <v>1</v>
       </c>
       <c r="BM9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BN9" t="n">
         <v>2</v>
@@ -4432,7 +4432,7 @@
         <v>2</v>
       </c>
       <c r="BS9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BT9" t="n">
         <v>1</v>
@@ -4444,28 +4444,28 @@
         <v>1</v>
       </c>
       <c r="BW9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BX9" t="n">
         <v>2</v>
       </c>
       <c r="BY9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BZ9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CA9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CB9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CC9" t="n">
         <v>2</v>
       </c>
       <c r="CD9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE9" t="n">
         <v>2</v>
@@ -4477,157 +4477,157 @@
         <v>4</v>
       </c>
       <c r="CH9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="CI9" t="n">
         <v>0</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CK9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CL9" t="n">
         <v>3</v>
       </c>
       <c r="CM9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CO9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CP9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CR9" t="n">
         <v>1</v>
       </c>
       <c r="CS9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="CT9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CU9" t="n">
         <v>0</v>
       </c>
       <c r="CV9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CW9" t="n">
+        <v>2</v>
+      </c>
+      <c r="CX9" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY9" t="n">
+        <v>1</v>
+      </c>
+      <c r="CZ9" t="n">
+        <v>2</v>
+      </c>
+      <c r="DA9" t="n">
+        <v>2</v>
+      </c>
+      <c r="DB9" t="n">
+        <v>1</v>
+      </c>
+      <c r="DC9" t="n">
+        <v>2</v>
+      </c>
+      <c r="DD9" t="n">
         <v>4</v>
       </c>
-      <c r="CX9" t="n">
-        <v>2</v>
-      </c>
-      <c r="CY9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CZ9" t="n">
-        <v>1</v>
-      </c>
-      <c r="DA9" t="n">
-        <v>1</v>
-      </c>
-      <c r="DB9" t="n">
-        <v>1</v>
-      </c>
-      <c r="DC9" t="n">
-        <v>1</v>
-      </c>
-      <c r="DD9" t="n">
-        <v>3</v>
-      </c>
       <c r="DE9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DF9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DG9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DH9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="DI9" t="n">
         <v>0</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="DK9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DL9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DM9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="DN9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="DP9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="DQ9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="DR9" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="DS9" t="n">
         <v>0</v>
       </c>
       <c r="DT9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU9" t="n">
         <v>2</v>
       </c>
       <c r="DV9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DW9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DX9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="DY9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="DZ9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EA9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="EB9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EC9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="ED9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="EE9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EF9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="EG9" t="n">
         <v>1</v>
@@ -4639,21 +4639,460 @@
         <v>0</v>
       </c>
       <c r="EJ9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EK9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="EL9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EM9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="EN9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="EO9" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Victor Bethlem</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>3</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>2</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>2</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>1</v>
+      </c>
+      <c r="CB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC10" t="n">
+        <v>2</v>
+      </c>
+      <c r="CD10" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE10" t="n">
+        <v>2</v>
+      </c>
+      <c r="CF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>4</v>
+      </c>
+      <c r="CH10" t="n">
+        <v>3</v>
+      </c>
+      <c r="CI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>2</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>3</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN10" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO10" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP10" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR10" t="n">
+        <v>1</v>
+      </c>
+      <c r="CS10" t="n">
+        <v>2</v>
+      </c>
+      <c r="CT10" t="n">
+        <v>3</v>
+      </c>
+      <c r="CU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV10" t="n">
+        <v>1</v>
+      </c>
+      <c r="CW10" t="n">
+        <v>4</v>
+      </c>
+      <c r="CX10" t="n">
+        <v>2</v>
+      </c>
+      <c r="CY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ10" t="n">
+        <v>1</v>
+      </c>
+      <c r="DA10" t="n">
+        <v>1</v>
+      </c>
+      <c r="DB10" t="n">
+        <v>1</v>
+      </c>
+      <c r="DC10" t="n">
+        <v>1</v>
+      </c>
+      <c r="DD10" t="n">
+        <v>3</v>
+      </c>
+      <c r="DE10" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF10" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH10" t="n">
+        <v>2</v>
+      </c>
+      <c r="DI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ10" t="n">
+        <v>2</v>
+      </c>
+      <c r="DK10" t="n">
+        <v>1</v>
+      </c>
+      <c r="DL10" t="n">
+        <v>1</v>
+      </c>
+      <c r="DM10" t="n">
+        <v>3</v>
+      </c>
+      <c r="DN10" t="n">
+        <v>1</v>
+      </c>
+      <c r="DO10" t="n">
+        <v>2</v>
+      </c>
+      <c r="DP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ10" t="n">
+        <v>3</v>
+      </c>
+      <c r="DR10" t="n">
+        <v>1</v>
+      </c>
+      <c r="DS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT10" t="n">
+        <v>1</v>
+      </c>
+      <c r="DU10" t="n">
+        <v>2</v>
+      </c>
+      <c r="DV10" t="n">
+        <v>3</v>
+      </c>
+      <c r="DW10" t="n">
+        <v>1</v>
+      </c>
+      <c r="DX10" t="n">
+        <v>2</v>
+      </c>
+      <c r="DY10" t="n">
+        <v>2</v>
+      </c>
+      <c r="DZ10" t="n">
+        <v>1</v>
+      </c>
+      <c r="EA10" t="n">
+        <v>1</v>
+      </c>
+      <c r="EB10" t="n">
+        <v>1</v>
+      </c>
+      <c r="EC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED10" t="n">
+        <v>2</v>
+      </c>
+      <c r="EE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF10" t="n">
+        <v>1</v>
+      </c>
+      <c r="EG10" t="n">
+        <v>1</v>
+      </c>
+      <c r="EH10" t="n">
+        <v>2</v>
+      </c>
+      <c r="EI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ10" t="n">
+        <v>1</v>
+      </c>
+      <c r="EK10" t="n">
+        <v>1</v>
+      </c>
+      <c r="EL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM10" t="n">
+        <v>2</v>
+      </c>
+      <c r="EN10" t="n">
+        <v>1</v>
+      </c>
+      <c r="EO10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4668,7 +5107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM9"/>
+  <dimension ref="A1:BM10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5335,177 +5774,177 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ana Leticia Xavier</t>
+          <t>Rafaela Albano Ribeiro</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>x</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>X</t>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>x</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>x</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>x</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>X</t>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>x</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>x</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>x</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>X</t>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>x</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>x</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>x</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>x</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>X</t>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>x</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>x</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>x</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>x</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>x</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>X</t>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>x</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>x</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>x</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>x</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="BC4" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="BE4" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="BF4" t="inlineStr">
-        <is>
-          <t>X</t>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>x</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>x</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="BL4" t="inlineStr">
-        <is>
-          <t>X</t>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>x</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Gustavo Marini</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
+          <t>Ana Leticia Xavier</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -5530,12 +5969,12 @@
           <t>X</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -5555,7 +5994,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -5580,12 +6019,12 @@
           <t>X</t>
         </is>
       </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -5635,7 +6074,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="BB5" t="inlineStr">
+      <c r="BC5" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -5645,7 +6084,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr">
+      <c r="BF5" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -5660,7 +6099,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="BM5" t="inlineStr">
+      <c r="BL5" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -5669,10 +6108,10 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Marcio</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
+          <t>Gustavo Marini</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -5682,7 +6121,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -5697,12 +6136,12 @@
           <t>X</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -5722,7 +6161,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -5747,12 +6186,12 @@
           <t>X</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -5777,7 +6216,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="AS6" t="inlineStr">
+      <c r="AR6" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -5817,7 +6256,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="BI6" t="inlineStr">
+      <c r="BH6" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -5827,7 +6266,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="BL6" t="inlineStr">
+      <c r="BM6" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -5836,10 +6275,10 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Pedro Thedim</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
+          <t>Marcio</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -5904,7 +6343,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -5914,171 +6353,171 @@
           <t>X</t>
         </is>
       </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>x</t>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>x</t>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="BF7" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="BH7" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="BK7" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="BM7" t="inlineStr">
-        <is>
-          <t>x</t>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Rafael Souto</t>
+          <t>Pedro Thedim</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>x</t>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>x</t>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
@@ -6136,7 +6575,7 @@
           <t>x</t>
         </is>
       </c>
-      <c r="BC8" t="inlineStr">
+      <c r="BB8" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -6151,17 +6590,17 @@
           <t>x</t>
         </is>
       </c>
-      <c r="BI8" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="BJ8" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="BL8" t="inlineStr">
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -6170,165 +6609,332 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Rafael Souto</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>Victor Bethlem</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="BB9" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="BE9" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="BI9" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="BJ9" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="BM9" t="inlineStr">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="BJ10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="BM10" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -6345,7 +6951,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6402,100 +7008,117 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ana Leticia Xavier</t>
+          <t>Rafaela Albano Ribeiro</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kylian Mbappé</t>
+          <t>Julián Álvarez</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>Argentina</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Gustavo Marini</t>
+          <t>Ana Leticia Xavier</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Danilo Santos</t>
+          <t>Kylian Mbappé</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Espanha</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Marcio</t>
+          <t>Gustavo Marini</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Harry Kane</t>
+          <t>Danilo Santos</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>Brasil</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Pedro Thedim</t>
+          <t>Marcio</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Kylian Mbappé</t>
+          <t>Harry Kane</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Franca</t>
+          <t>Espanha</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Rafael Souto</t>
+          <t>Pedro Thedim</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Julián Álvarez</t>
+          <t>Kylian Mbappé</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Franca</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Rafael Souto</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Julián Álvarez</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>Victor Bethlem</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Kylian Mbappé</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Inglaterra</t>
         </is>

--- a/apostas/Bolao_Copa2026_TurimMFO - Consolidada.xlsx
+++ b/apostas/Bolao_Copa2026_TurimMFO - Consolidada.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EO10"/>
+  <dimension ref="A1:EO12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1148,7 +1148,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Leonardo Martins</t>
+          <t>Ana Beatriz Ferreira</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -1158,73 +1158,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R2" t="n">
         <v>2</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V2" t="n">
         <v>1</v>
       </c>
       <c r="W2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA2" t="n">
         <v>1</v>
@@ -1233,89 +1233,89 @@
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AD2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD2" t="n">
         <v>4</v>
       </c>
-      <c r="AG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>1</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>2</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>3</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>2</v>
-      </c>
       <c r="BE2" t="n">
         <v>0</v>
       </c>
@@ -1323,34 +1323,34 @@
         <v>1</v>
       </c>
       <c r="BG2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BH2" t="n">
         <v>0</v>
       </c>
       <c r="BI2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BJ2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BK2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BL2" t="n">
         <v>1</v>
       </c>
       <c r="BM2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BN2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BO2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BP2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ2" t="n">
         <v>2</v>
@@ -1359,25 +1359,25 @@
         <v>1</v>
       </c>
       <c r="BS2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BU2" t="n">
         <v>3</v>
       </c>
       <c r="BV2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BX2" t="n">
         <v>1</v>
       </c>
       <c r="BY2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BZ2" t="n">
         <v>2</v>
@@ -1389,13 +1389,13 @@
         <v>0</v>
       </c>
       <c r="CC2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CD2" t="n">
         <v>2</v>
       </c>
       <c r="CE2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF2" t="n">
         <v>0</v>
@@ -1410,19 +1410,19 @@
         <v>0</v>
       </c>
       <c r="CJ2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CK2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CL2" t="n">
         <v>3</v>
       </c>
       <c r="CM2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CO2" t="n">
         <v>0</v>
@@ -1431,151 +1431,151 @@
         <v>1</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CR2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CS2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CT2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CU2" t="n">
         <v>0</v>
       </c>
       <c r="CV2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CW2" t="n">
         <v>2</v>
       </c>
       <c r="CX2" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY2" t="n">
+        <v>1</v>
+      </c>
+      <c r="CZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA2" t="n">
+        <v>2</v>
+      </c>
+      <c r="DB2" t="n">
+        <v>1</v>
+      </c>
+      <c r="DC2" t="n">
+        <v>2</v>
+      </c>
+      <c r="DD2" t="n">
+        <v>1</v>
+      </c>
+      <c r="DE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF2" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>2</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>1</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>1</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>2</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>6</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>1</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>1</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>3</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>2</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>3</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>3</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED2" t="n">
+        <v>2</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>2</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>2</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>3</v>
+      </c>
+      <c r="EI2" t="n">
+        <v>1</v>
+      </c>
+      <c r="EJ2" t="n">
+        <v>1</v>
+      </c>
+      <c r="EK2" t="n">
         <v>4</v>
       </c>
-      <c r="CY2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CZ2" t="n">
-        <v>2</v>
-      </c>
-      <c r="DA2" t="n">
-        <v>2</v>
-      </c>
-      <c r="DB2" t="n">
-        <v>1</v>
-      </c>
-      <c r="DC2" t="n">
-        <v>2</v>
-      </c>
-      <c r="DD2" t="n">
-        <v>2</v>
-      </c>
-      <c r="DE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DF2" t="n">
-        <v>2</v>
-      </c>
-      <c r="DG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DH2" t="n">
-        <v>1</v>
-      </c>
-      <c r="DI2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ2" t="n">
-        <v>3</v>
-      </c>
-      <c r="DK2" t="n">
-        <v>1</v>
-      </c>
-      <c r="DL2" t="n">
-        <v>1</v>
-      </c>
-      <c r="DM2" t="n">
-        <v>2</v>
-      </c>
-      <c r="DN2" t="n">
-        <v>1</v>
-      </c>
-      <c r="DO2" t="n">
-        <v>1</v>
-      </c>
-      <c r="DP2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DQ2" t="n">
-        <v>3</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>3</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>1</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>4</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>3</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>2</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>1</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>2</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>1</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>1</v>
-      </c>
-      <c r="ED2" t="n">
-        <v>2</v>
-      </c>
-      <c r="EE2" t="n">
-        <v>2</v>
-      </c>
-      <c r="EF2" t="n">
-        <v>1</v>
-      </c>
-      <c r="EG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="EH2" t="n">
-        <v>3</v>
-      </c>
-      <c r="EI2" t="n">
-        <v>1</v>
-      </c>
-      <c r="EJ2" t="n">
-        <v>1</v>
-      </c>
-      <c r="EK2" t="n">
-        <v>3</v>
-      </c>
       <c r="EL2" t="n">
         <v>0</v>
       </c>
       <c r="EM2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="EN2" t="n">
         <v>2</v>
@@ -1587,17 +1587,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Pedro Brandão</t>
+          <t>Leonardo Martins</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -1606,10 +1606,10 @@
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
         <v>1</v>
@@ -1621,13 +1621,13 @@
         <v>2</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -1645,22 +1645,22 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
         <v>2</v>
@@ -1675,10 +1675,10 @@
         <v>2</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF3" t="n">
         <v>4</v>
@@ -1687,7 +1687,7 @@
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
         <v>2</v>
@@ -1708,16 +1708,16 @@
         <v>1</v>
       </c>
       <c r="AO3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS3" t="n">
         <v>1</v>
@@ -1732,7 +1732,7 @@
         <v>1</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX3" t="n">
         <v>4</v>
@@ -1741,16 +1741,16 @@
         <v>0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BC3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD3" t="n">
         <v>2</v>
@@ -1762,34 +1762,34 @@
         <v>1</v>
       </c>
       <c r="BG3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BH3" t="n">
         <v>0</v>
       </c>
       <c r="BI3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BK3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BL3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BM3" t="n">
         <v>0</v>
       </c>
       <c r="BN3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BO3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ3" t="n">
         <v>2</v>
@@ -1801,16 +1801,16 @@
         <v>1</v>
       </c>
       <c r="BT3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BV3" t="n">
         <v>2</v>
       </c>
       <c r="BW3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BX3" t="n">
         <v>1</v>
@@ -1831,7 +1831,7 @@
         <v>2</v>
       </c>
       <c r="CD3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CE3" t="n">
         <v>0</v>
@@ -1840,128 +1840,128 @@
         <v>0</v>
       </c>
       <c r="CG3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CH3" t="n">
+        <v>5</v>
+      </c>
+      <c r="CI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ3" t="n">
+        <v>2</v>
+      </c>
+      <c r="CK3" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL3" t="n">
+        <v>3</v>
+      </c>
+      <c r="CM3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN3" t="n">
+        <v>3</v>
+      </c>
+      <c r="CO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP3" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ3" t="n">
+        <v>2</v>
+      </c>
+      <c r="CR3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS3" t="n">
+        <v>2</v>
+      </c>
+      <c r="CT3" t="n">
+        <v>2</v>
+      </c>
+      <c r="CU3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW3" t="n">
+        <v>2</v>
+      </c>
+      <c r="CX3" t="n">
         <v>4</v>
       </c>
-      <c r="CI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CJ3" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK3" t="n">
-        <v>2</v>
-      </c>
-      <c r="CL3" t="n">
-        <v>3</v>
-      </c>
-      <c r="CM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN3" t="n">
-        <v>2</v>
-      </c>
-      <c r="CO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP3" t="n">
-        <v>1</v>
-      </c>
-      <c r="CQ3" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR3" t="n">
-        <v>1</v>
-      </c>
-      <c r="CS3" t="n">
-        <v>2</v>
-      </c>
-      <c r="CT3" t="n">
-        <v>3</v>
-      </c>
-      <c r="CU3" t="n">
-        <v>1</v>
-      </c>
-      <c r="CV3" t="n">
-        <v>1</v>
-      </c>
-      <c r="CW3" t="n">
+      <c r="CY3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ3" t="n">
+        <v>2</v>
+      </c>
+      <c r="DA3" t="n">
+        <v>2</v>
+      </c>
+      <c r="DB3" t="n">
+        <v>1</v>
+      </c>
+      <c r="DC3" t="n">
+        <v>2</v>
+      </c>
+      <c r="DD3" t="n">
+        <v>2</v>
+      </c>
+      <c r="DE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF3" t="n">
+        <v>2</v>
+      </c>
+      <c r="DG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH3" t="n">
+        <v>1</v>
+      </c>
+      <c r="DI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ3" t="n">
+        <v>3</v>
+      </c>
+      <c r="DK3" t="n">
+        <v>1</v>
+      </c>
+      <c r="DL3" t="n">
+        <v>1</v>
+      </c>
+      <c r="DM3" t="n">
+        <v>2</v>
+      </c>
+      <c r="DN3" t="n">
+        <v>1</v>
+      </c>
+      <c r="DO3" t="n">
+        <v>1</v>
+      </c>
+      <c r="DP3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ3" t="n">
+        <v>3</v>
+      </c>
+      <c r="DR3" t="n">
+        <v>3</v>
+      </c>
+      <c r="DS3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT3" t="n">
+        <v>1</v>
+      </c>
+      <c r="DU3" t="n">
         <v>4</v>
       </c>
-      <c r="CX3" t="n">
-        <v>3</v>
-      </c>
-      <c r="CY3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CZ3" t="n">
-        <v>2</v>
-      </c>
-      <c r="DA3" t="n">
-        <v>2</v>
-      </c>
-      <c r="DB3" t="n">
-        <v>2</v>
-      </c>
-      <c r="DC3" t="n">
-        <v>3</v>
-      </c>
-      <c r="DD3" t="n">
-        <v>2</v>
-      </c>
-      <c r="DE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="DF3" t="n">
-        <v>2</v>
-      </c>
-      <c r="DG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="DH3" t="n">
-        <v>2</v>
-      </c>
-      <c r="DI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ3" t="n">
-        <v>1</v>
-      </c>
-      <c r="DK3" t="n">
-        <v>1</v>
-      </c>
-      <c r="DL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="DM3" t="n">
-        <v>2</v>
-      </c>
-      <c r="DN3" t="n">
-        <v>0</v>
-      </c>
-      <c r="DO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="DP3" t="n">
-        <v>0</v>
-      </c>
-      <c r="DQ3" t="n">
-        <v>3</v>
-      </c>
-      <c r="DR3" t="n">
-        <v>2</v>
-      </c>
-      <c r="DS3" t="n">
-        <v>0</v>
-      </c>
-      <c r="DT3" t="n">
-        <v>1</v>
-      </c>
-      <c r="DU3" t="n">
-        <v>2</v>
-      </c>
       <c r="DV3" t="n">
         <v>3</v>
       </c>
@@ -1972,16 +1972,16 @@
         <v>2</v>
       </c>
       <c r="DY3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DZ3" t="n">
         <v>1</v>
       </c>
       <c r="EA3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="EB3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EC3" t="n">
         <v>1</v>
@@ -1990,56 +1990,56 @@
         <v>2</v>
       </c>
       <c r="EE3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="EF3" t="n">
         <v>1</v>
       </c>
       <c r="EG3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EH3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="EI3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EK3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="EL3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EM3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="EN3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="EO3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Rafaela Albano Ribeiro</t>
+          <t>Mariella Lage</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
         <v>2</v>
@@ -2051,13 +2051,13 @@
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>1</v>
@@ -2069,7 +2069,7 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -2084,10 +2084,10 @@
         <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V4" t="n">
         <v>1</v>
@@ -2105,7 +2105,7 @@
         <v>2</v>
       </c>
       <c r="AA4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
@@ -2117,7 +2117,7 @@
         <v>1</v>
       </c>
       <c r="AE4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF4" t="n">
         <v>5</v>
@@ -2129,7 +2129,7 @@
         <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ4" t="n">
         <v>3</v>
@@ -2141,149 +2141,149 @@
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN4" t="n">
         <v>1</v>
       </c>
       <c r="AO4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AP4" t="n">
         <v>1</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR4" t="n">
         <v>1</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>3</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>2</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>1</v>
+      </c>
+      <c r="CB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC4" t="n">
+        <v>2</v>
+      </c>
+      <c r="CD4" t="n">
+        <v>2</v>
+      </c>
+      <c r="CE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG4" t="n">
+        <v>2</v>
+      </c>
+      <c r="CH4" t="n">
         <v>4</v>
       </c>
-      <c r="AY4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>3</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>2</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>2</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>2</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>3</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BX4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ4" t="n">
-        <v>2</v>
-      </c>
-      <c r="CA4" t="n">
-        <v>1</v>
-      </c>
-      <c r="CB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CC4" t="n">
-        <v>1</v>
-      </c>
-      <c r="CD4" t="n">
-        <v>1</v>
-      </c>
-      <c r="CE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG4" t="n">
-        <v>3</v>
-      </c>
-      <c r="CH4" t="n">
-        <v>5</v>
-      </c>
       <c r="CI4" t="n">
         <v>0</v>
       </c>
@@ -2291,7 +2291,7 @@
         <v>1</v>
       </c>
       <c r="CK4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CL4" t="n">
         <v>2</v>
@@ -2309,19 +2309,19 @@
         <v>1</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CR4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CS4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CT4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CU4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CV4" t="n">
         <v>0</v>
@@ -2330,7 +2330,7 @@
         <v>3</v>
       </c>
       <c r="CX4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CY4" t="n">
         <v>0</v>
@@ -2339,16 +2339,16 @@
         <v>2</v>
       </c>
       <c r="DA4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="DB4" t="n">
         <v>1</v>
       </c>
       <c r="DC4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="DD4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="DE4" t="n">
         <v>0</v>
@@ -2360,7 +2360,7 @@
         <v>0</v>
       </c>
       <c r="DH4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DI4" t="n">
         <v>0</v>
@@ -2375,7 +2375,7 @@
         <v>1</v>
       </c>
       <c r="DM4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DN4" t="n">
         <v>0</v>
@@ -2396,13 +2396,13 @@
         <v>0</v>
       </c>
       <c r="DT4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="DV4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="DW4" t="n">
         <v>0</v>
@@ -2411,61 +2411,61 @@
         <v>2</v>
       </c>
       <c r="DY4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DZ4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="EA4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="EB4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EC4" t="n">
         <v>1</v>
       </c>
       <c r="ED4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="EE4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EF4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="EG4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="EH4" t="n">
         <v>2</v>
       </c>
       <c r="EI4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EJ4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EK4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="EL4" t="n">
         <v>0</v>
       </c>
       <c r="EM4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="EN4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="EO4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ana Leticia Xavier</t>
+          <t>Pedro Brandão</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -2481,10 +2481,10 @@
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
         <v>2</v>
@@ -2493,19 +2493,19 @@
         <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -2514,31 +2514,31 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R5" t="n">
         <v>2</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
         <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>2</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z5" t="n">
         <v>2</v>
@@ -2547,13 +2547,13 @@
         <v>1</v>
       </c>
       <c r="AB5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
         <v>2</v>
@@ -2568,7 +2568,7 @@
         <v>1</v>
       </c>
       <c r="AI5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AJ5" t="n">
         <v>3</v>
@@ -2580,7 +2580,7 @@
         <v>2</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN5" t="n">
         <v>1</v>
@@ -2598,7 +2598,7 @@
         <v>1</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT5" t="n">
         <v>1</v>
@@ -2607,7 +2607,7 @@
         <v>1</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW5" t="n">
         <v>0</v>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA5" t="n">
         <v>1</v>
       </c>
       <c r="BB5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BC5" t="n">
         <v>1</v>
@@ -2646,25 +2646,25 @@
         <v>0</v>
       </c>
       <c r="BI5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BJ5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BK5" t="n">
         <v>1</v>
       </c>
       <c r="BL5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BM5" t="n">
         <v>0</v>
       </c>
       <c r="BN5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BO5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BP5" t="n">
         <v>1</v>
@@ -2685,7 +2685,7 @@
         <v>2</v>
       </c>
       <c r="BV5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BW5" t="n">
         <v>1</v>
@@ -2694,25 +2694,25 @@
         <v>1</v>
       </c>
       <c r="BY5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BZ5" t="n">
         <v>2</v>
       </c>
       <c r="CA5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CB5" t="n">
         <v>0</v>
       </c>
       <c r="CC5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CD5" t="n">
         <v>1</v>
       </c>
       <c r="CE5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF5" t="n">
         <v>0</v>
@@ -2721,7 +2721,7 @@
         <v>3</v>
       </c>
       <c r="CH5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CI5" t="n">
         <v>0</v>
@@ -2748,7 +2748,7 @@
         <v>1</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CR5" t="n">
         <v>1</v>
@@ -2766,10 +2766,10 @@
         <v>1</v>
       </c>
       <c r="CW5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CX5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="CY5" t="n">
         <v>0</v>
@@ -2781,7 +2781,7 @@
         <v>2</v>
       </c>
       <c r="DB5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DC5" t="n">
         <v>3</v>
@@ -2793,7 +2793,7 @@
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="DG5" t="n">
         <v>0</v>
@@ -2805,7 +2805,7 @@
         <v>0</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="DK5" t="n">
         <v>1</v>
@@ -2814,49 +2814,49 @@
         <v>0</v>
       </c>
       <c r="DM5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DN5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DP5" t="n">
         <v>0</v>
       </c>
       <c r="DQ5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="DR5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="DS5" t="n">
         <v>0</v>
       </c>
       <c r="DT5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="DV5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="DW5" t="n">
         <v>0</v>
       </c>
       <c r="DX5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="DY5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DZ5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="EA5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="EB5" t="n">
         <v>0</v>
@@ -2874,10 +2874,10 @@
         <v>1</v>
       </c>
       <c r="EG5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EH5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="EI5" t="n">
         <v>0</v>
@@ -2892,10 +2892,10 @@
         <v>1</v>
       </c>
       <c r="EM5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="EN5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="EO5" t="n">
         <v>0</v>
@@ -2904,7 +2904,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Gustavo Marini</t>
+          <t>Rafaela Albano Ribeiro</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -2923,137 +2923,137 @@
         <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX6" t="n">
         <v>4</v>
       </c>
-      <c r="U6" t="n">
-        <v>2</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1</v>
-      </c>
-      <c r="X6" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>6</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>3</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>3</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>2</v>
-      </c>
       <c r="AY6" t="n">
         <v>0</v>
       </c>
@@ -3061,296 +3061,296 @@
         <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BC6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BE6" t="n">
         <v>1</v>
       </c>
       <c r="BF6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BG6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>3</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>2</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>1</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>3</v>
+      </c>
+      <c r="CH6" t="n">
+        <v>5</v>
+      </c>
+      <c r="CI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ6" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>2</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN6" t="n">
+        <v>3</v>
+      </c>
+      <c r="CO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP6" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ6" t="n">
+        <v>3</v>
+      </c>
+      <c r="CR6" t="n">
+        <v>1</v>
+      </c>
+      <c r="CS6" t="n">
+        <v>3</v>
+      </c>
+      <c r="CT6" t="n">
+        <v>2</v>
+      </c>
+      <c r="CU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW6" t="n">
+        <v>3</v>
+      </c>
+      <c r="CX6" t="n">
         <v>4</v>
       </c>
-      <c r="BH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ6" t="n">
+      <c r="CY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ6" t="n">
+        <v>2</v>
+      </c>
+      <c r="DA6" t="n">
+        <v>2</v>
+      </c>
+      <c r="DB6" t="n">
+        <v>1</v>
+      </c>
+      <c r="DC6" t="n">
+        <v>2</v>
+      </c>
+      <c r="DD6" t="n">
+        <v>2</v>
+      </c>
+      <c r="DE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF6" t="n">
+        <v>2</v>
+      </c>
+      <c r="DG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH6" t="n">
+        <v>1</v>
+      </c>
+      <c r="DI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ6" t="n">
+        <v>2</v>
+      </c>
+      <c r="DK6" t="n">
+        <v>1</v>
+      </c>
+      <c r="DL6" t="n">
+        <v>1</v>
+      </c>
+      <c r="DM6" t="n">
+        <v>1</v>
+      </c>
+      <c r="DN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO6" t="n">
+        <v>1</v>
+      </c>
+      <c r="DP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ6" t="n">
+        <v>3</v>
+      </c>
+      <c r="DR6" t="n">
+        <v>3</v>
+      </c>
+      <c r="DS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU6" t="n">
+        <v>3</v>
+      </c>
+      <c r="DV6" t="n">
         <v>4</v>
       </c>
-      <c r="BK6" t="n">
-        <v>2</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>3</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>3</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>2</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>2</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>1</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>1</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>3</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>1</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>1</v>
-      </c>
-      <c r="BX6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ6" t="n">
-        <v>3</v>
-      </c>
-      <c r="CA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB6" t="n">
-        <v>1</v>
-      </c>
-      <c r="CC6" t="n">
-        <v>2</v>
-      </c>
-      <c r="CD6" t="n">
-        <v>2</v>
-      </c>
-      <c r="CE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF6" t="n">
-        <v>2</v>
-      </c>
-      <c r="CG6" t="n">
+      <c r="DW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX6" t="n">
+        <v>2</v>
+      </c>
+      <c r="DY6" t="n">
+        <v>1</v>
+      </c>
+      <c r="DZ6" t="n">
+        <v>1</v>
+      </c>
+      <c r="EA6" t="n">
+        <v>2</v>
+      </c>
+      <c r="EB6" t="n">
+        <v>1</v>
+      </c>
+      <c r="EC6" t="n">
+        <v>1</v>
+      </c>
+      <c r="ED6" t="n">
+        <v>1</v>
+      </c>
+      <c r="EE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF6" t="n">
+        <v>1</v>
+      </c>
+      <c r="EG6" t="n">
+        <v>2</v>
+      </c>
+      <c r="EH6" t="n">
+        <v>2</v>
+      </c>
+      <c r="EI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ6" t="n">
+        <v>1</v>
+      </c>
+      <c r="EK6" t="n">
+        <v>3</v>
+      </c>
+      <c r="EL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM6" t="n">
         <v>4</v>
       </c>
-      <c r="CH6" t="n">
-        <v>4</v>
-      </c>
-      <c r="CI6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CJ6" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK6" t="n">
-        <v>3</v>
-      </c>
-      <c r="CL6" t="n">
-        <v>2</v>
-      </c>
-      <c r="CM6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN6" t="n">
-        <v>2</v>
-      </c>
-      <c r="CO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP6" t="n">
-        <v>2</v>
-      </c>
-      <c r="CQ6" t="n">
-        <v>2</v>
-      </c>
-      <c r="CR6" t="n">
-        <v>2</v>
-      </c>
-      <c r="CS6" t="n">
-        <v>3</v>
-      </c>
-      <c r="CT6" t="n">
-        <v>3</v>
-      </c>
-      <c r="CU6" t="n">
-        <v>1</v>
-      </c>
-      <c r="CV6" t="n">
-        <v>1</v>
-      </c>
-      <c r="CW6" t="n">
-        <v>2</v>
-      </c>
-      <c r="CX6" t="n">
-        <v>3</v>
-      </c>
-      <c r="CY6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CZ6" t="n">
-        <v>1</v>
-      </c>
-      <c r="DA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DC6" t="n">
-        <v>2</v>
-      </c>
-      <c r="DD6" t="n">
-        <v>3</v>
-      </c>
-      <c r="DE6" t="n">
-        <v>3</v>
-      </c>
-      <c r="DF6" t="n">
-        <v>3</v>
-      </c>
-      <c r="DG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DI6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ6" t="n">
-        <v>2</v>
-      </c>
-      <c r="DK6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DM6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DN6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DP6" t="n">
-        <v>1</v>
-      </c>
-      <c r="DQ6" t="n">
-        <v>4</v>
-      </c>
-      <c r="DR6" t="n">
-        <v>2</v>
-      </c>
-      <c r="DS6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DT6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DU6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DW6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX6" t="n">
-        <v>1</v>
-      </c>
-      <c r="DY6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DZ6" t="n">
-        <v>1</v>
-      </c>
-      <c r="EA6" t="n">
-        <v>1</v>
-      </c>
-      <c r="EB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="EC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="ED6" t="n">
-        <v>1</v>
-      </c>
-      <c r="EE6" t="n">
-        <v>2</v>
-      </c>
-      <c r="EF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="EG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="EH6" t="n">
-        <v>2</v>
-      </c>
-      <c r="EI6" t="n">
-        <v>0</v>
-      </c>
-      <c r="EJ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="EK6" t="n">
-        <v>3</v>
-      </c>
-      <c r="EL6" t="n">
-        <v>1</v>
-      </c>
-      <c r="EM6" t="n">
-        <v>2</v>
-      </c>
       <c r="EN6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="EO6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Marcio</t>
+          <t>Ana Leticia Xavier</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
@@ -3359,10 +3359,10 @@
         <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
         <v>2</v>
@@ -3380,10 +3380,10 @@
         <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -3392,16 +3392,16 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R7" t="n">
         <v>2</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U7" t="n">
         <v>1</v>
@@ -3410,25 +3410,25 @@
         <v>2</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA7" t="n">
         <v>1</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD7" t="n">
         <v>1</v>
@@ -3443,10 +3443,10 @@
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ7" t="n">
         <v>3</v>
@@ -3455,10 +3455,10 @@
         <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
         <v>1</v>
@@ -3467,245 +3467,245 @@
         <v>2</v>
       </c>
       <c r="AP7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU7" t="n">
         <v>1</v>
       </c>
       <c r="AV7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW7" t="n">
         <v>0</v>
       </c>
       <c r="AX7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>3</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>2</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>1</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>3</v>
+      </c>
+      <c r="CH7" t="n">
         <v>5</v>
       </c>
-      <c r="AY7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>2</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>2</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>3</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>1</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>2</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>2</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>2</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>1</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>3</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>2</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>2</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ7" t="n">
-        <v>2</v>
-      </c>
-      <c r="CA7" t="n">
-        <v>1</v>
-      </c>
-      <c r="CB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CC7" t="n">
-        <v>1</v>
-      </c>
-      <c r="CD7" t="n">
-        <v>1</v>
-      </c>
-      <c r="CE7" t="n">
-        <v>1</v>
-      </c>
-      <c r="CF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG7" t="n">
-        <v>3</v>
-      </c>
-      <c r="CH7" t="n">
+      <c r="CI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>2</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>3</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN7" t="n">
+        <v>2</v>
+      </c>
+      <c r="CO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP7" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ7" t="n">
+        <v>2</v>
+      </c>
+      <c r="CR7" t="n">
+        <v>1</v>
+      </c>
+      <c r="CS7" t="n">
+        <v>2</v>
+      </c>
+      <c r="CT7" t="n">
+        <v>3</v>
+      </c>
+      <c r="CU7" t="n">
+        <v>1</v>
+      </c>
+      <c r="CV7" t="n">
+        <v>1</v>
+      </c>
+      <c r="CW7" t="n">
+        <v>3</v>
+      </c>
+      <c r="CX7" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ7" t="n">
+        <v>2</v>
+      </c>
+      <c r="DA7" t="n">
+        <v>2</v>
+      </c>
+      <c r="DB7" t="n">
+        <v>1</v>
+      </c>
+      <c r="DC7" t="n">
+        <v>3</v>
+      </c>
+      <c r="DD7" t="n">
+        <v>2</v>
+      </c>
+      <c r="DE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF7" t="n">
+        <v>3</v>
+      </c>
+      <c r="DG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH7" t="n">
+        <v>2</v>
+      </c>
+      <c r="DI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ7" t="n">
+        <v>2</v>
+      </c>
+      <c r="DK7" t="n">
+        <v>1</v>
+      </c>
+      <c r="DL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM7" t="n">
+        <v>1</v>
+      </c>
+      <c r="DN7" t="n">
+        <v>1</v>
+      </c>
+      <c r="DO7" t="n">
+        <v>1</v>
+      </c>
+      <c r="DP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ7" t="n">
         <v>4</v>
       </c>
-      <c r="CI7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CK7" t="n">
-        <v>2</v>
-      </c>
-      <c r="CL7" t="n">
-        <v>3</v>
-      </c>
-      <c r="CM7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN7" t="n">
-        <v>3</v>
-      </c>
-      <c r="CO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ7" t="n">
-        <v>2</v>
-      </c>
-      <c r="CR7" t="n">
-        <v>1</v>
-      </c>
-      <c r="CS7" t="n">
-        <v>2</v>
-      </c>
-      <c r="CT7" t="n">
-        <v>3</v>
-      </c>
-      <c r="CU7" t="n">
-        <v>1</v>
-      </c>
-      <c r="CV7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CW7" t="n">
-        <v>2</v>
-      </c>
-      <c r="CX7" t="n">
-        <v>3</v>
-      </c>
-      <c r="CY7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CZ7" t="n">
-        <v>2</v>
-      </c>
-      <c r="DA7" t="n">
-        <v>1</v>
-      </c>
-      <c r="DB7" t="n">
-        <v>1</v>
-      </c>
-      <c r="DC7" t="n">
-        <v>2</v>
-      </c>
-      <c r="DD7" t="n">
-        <v>1</v>
-      </c>
-      <c r="DE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DF7" t="n">
-        <v>2</v>
-      </c>
-      <c r="DG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DH7" t="n">
-        <v>2</v>
-      </c>
-      <c r="DI7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ7" t="n">
-        <v>2</v>
-      </c>
-      <c r="DK7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DM7" t="n">
-        <v>1</v>
-      </c>
-      <c r="DN7" t="n">
-        <v>1</v>
-      </c>
-      <c r="DO7" t="n">
-        <v>1</v>
-      </c>
-      <c r="DP7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DQ7" t="n">
-        <v>3</v>
-      </c>
       <c r="DR7" t="n">
         <v>3</v>
       </c>
@@ -3716,16 +3716,16 @@
         <v>0</v>
       </c>
       <c r="DU7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DV7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DW7" t="n">
         <v>0</v>
       </c>
       <c r="DX7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DY7" t="n">
         <v>0</v>
@@ -3737,7 +3737,7 @@
         <v>2</v>
       </c>
       <c r="EB7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EC7" t="n">
         <v>1</v>
@@ -3749,16 +3749,16 @@
         <v>1</v>
       </c>
       <c r="EF7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="EG7" t="n">
         <v>0</v>
       </c>
       <c r="EH7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="EI7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EJ7" t="n">
         <v>0</v>
@@ -3767,83 +3767,83 @@
         <v>2</v>
       </c>
       <c r="EL7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EM7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="EN7" t="n">
         <v>2</v>
       </c>
       <c r="EO7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Pedro Thedim</t>
+          <t>Gustavo Marini</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J8" t="n">
         <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R8" t="n">
         <v>2</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V8" t="n">
         <v>1</v>
@@ -3852,13 +3852,13 @@
         <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA8" t="n">
         <v>1</v>
@@ -3870,22 +3870,22 @@
         <v>2</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH8" t="n">
         <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ8" t="n">
         <v>3</v>
@@ -3894,7 +3894,7 @@
         <v>1</v>
       </c>
       <c r="AL8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
         <v>0</v>
@@ -3903,13 +3903,13 @@
         <v>0</v>
       </c>
       <c r="AO8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR8" t="n">
         <v>1</v>
@@ -3918,19 +3918,19 @@
         <v>0</v>
       </c>
       <c r="AT8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU8" t="n">
         <v>2</v>
       </c>
       <c r="AV8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AX8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AY8" t="n">
         <v>0</v>
@@ -3939,58 +3939,58 @@
         <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB8" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG8" t="n">
         <v>4</v>
       </c>
-      <c r="BC8" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>2</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>1</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>1</v>
-      </c>
       <c r="BH8" t="n">
         <v>0</v>
       </c>
       <c r="BI8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BK8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BL8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BM8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BN8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BO8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP8" t="n">
         <v>0</v>
       </c>
       <c r="BQ8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BR8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BS8" t="n">
         <v>1</v>
@@ -3999,7 +3999,7 @@
         <v>1</v>
       </c>
       <c r="BU8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BV8" t="n">
         <v>1</v>
@@ -4008,16 +4008,16 @@
         <v>1</v>
       </c>
       <c r="BX8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BY8" t="n">
         <v>0</v>
       </c>
       <c r="BZ8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="CA8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CB8" t="n">
         <v>1</v>
@@ -4026,52 +4026,52 @@
         <v>2</v>
       </c>
       <c r="CD8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CE8" t="n">
         <v>0</v>
       </c>
       <c r="CF8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CG8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CH8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="CI8" t="n">
         <v>0</v>
       </c>
       <c r="CJ8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CK8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CL8" t="n">
         <v>2</v>
       </c>
       <c r="CM8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CO8" t="n">
         <v>0</v>
       </c>
       <c r="CP8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CR8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CS8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="CT8" t="n">
         <v>3</v>
@@ -4080,91 +4080,91 @@
         <v>1</v>
       </c>
       <c r="CV8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CW8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CX8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="CY8" t="n">
         <v>0</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="DA8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DB8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="DC8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="DD8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DE8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="DF8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DG8" t="n">
         <v>0</v>
       </c>
       <c r="DH8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="DI8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DK8" t="n">
         <v>0</v>
       </c>
       <c r="DL8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DM8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="DN8" t="n">
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DP8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DQ8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DR8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="DS8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT8" t="n">
         <v>0</v>
       </c>
       <c r="DU8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="DW8" t="n">
         <v>0</v>
       </c>
       <c r="DX8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="DY8" t="n">
         <v>0</v>
@@ -4173,25 +4173,25 @@
         <v>1</v>
       </c>
       <c r="EA8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="EB8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EC8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="ED8" t="n">
         <v>1</v>
       </c>
       <c r="EE8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="EF8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="EG8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="EH8" t="n">
         <v>2</v>
@@ -4203,41 +4203,41 @@
         <v>0</v>
       </c>
       <c r="EK8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="EL8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EM8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="EN8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="EO8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Rafael Souto</t>
+          <t>Marcio</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -4249,74 +4249,74 @@
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K9" t="n">
         <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" t="n">
         <v>1</v>
       </c>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
+        <v>2</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V9" t="n">
+        <v>2</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF9" t="n">
         <v>4</v>
       </c>
-      <c r="R9" t="n">
-        <v>2</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1</v>
-      </c>
-      <c r="W9" t="n">
-        <v>2</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>6</v>
-      </c>
       <c r="AG9" t="n">
         <v>0</v>
       </c>
@@ -4327,7 +4327,7 @@
         <v>2</v>
       </c>
       <c r="AJ9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AK9" t="n">
         <v>0</v>
@@ -4336,7 +4336,7 @@
         <v>1</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN9" t="n">
         <v>1</v>
@@ -4348,25 +4348,25 @@
         <v>2</v>
       </c>
       <c r="AQ9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AR9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT9" t="n">
         <v>2</v>
       </c>
       <c r="AU9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AX9" t="n">
         <v>5</v>
@@ -4375,16 +4375,16 @@
         <v>0</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BC9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD9" t="n">
         <v>3</v>
@@ -4393,34 +4393,34 @@
         <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BG9" t="n">
         <v>2</v>
       </c>
       <c r="BH9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BI9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BJ9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BK9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BL9" t="n">
         <v>1</v>
       </c>
       <c r="BM9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BN9" t="n">
         <v>2</v>
       </c>
       <c r="BO9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP9" t="n">
         <v>0</v>
@@ -4429,19 +4429,19 @@
         <v>1</v>
       </c>
       <c r="BR9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BS9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BT9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU9" t="n">
         <v>3</v>
       </c>
       <c r="BV9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
@@ -4450,35 +4450,35 @@
         <v>2</v>
       </c>
       <c r="BY9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BZ9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CA9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CB9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CC9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CD9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CF9" t="n">
         <v>0</v>
       </c>
       <c r="CG9" t="n">
+        <v>3</v>
+      </c>
+      <c r="CH9" t="n">
         <v>4</v>
       </c>
-      <c r="CH9" t="n">
-        <v>6</v>
-      </c>
       <c r="CI9" t="n">
         <v>0</v>
       </c>
@@ -4486,16 +4486,16 @@
         <v>0</v>
       </c>
       <c r="CK9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CL9" t="n">
         <v>3</v>
       </c>
       <c r="CM9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CO9" t="n">
         <v>0</v>
@@ -4510,13 +4510,13 @@
         <v>1</v>
       </c>
       <c r="CS9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CT9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="CU9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CV9" t="n">
         <v>0</v>
@@ -4525,16 +4525,16 @@
         <v>2</v>
       </c>
       <c r="CX9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="CY9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CZ9" t="n">
         <v>2</v>
       </c>
       <c r="DA9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="DB9" t="n">
         <v>1</v>
@@ -4543,25 +4543,25 @@
         <v>2</v>
       </c>
       <c r="DD9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="DE9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="DF9" t="n">
         <v>2</v>
       </c>
       <c r="DG9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DH9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="DI9" t="n">
         <v>0</v>
       </c>
       <c r="DJ9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DK9" t="n">
         <v>0</v>
@@ -4573,19 +4573,19 @@
         <v>1</v>
       </c>
       <c r="DN9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DO9" t="n">
         <v>1</v>
       </c>
       <c r="DP9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="DQ9" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="DR9" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="DS9" t="n">
         <v>0</v>
@@ -4597,46 +4597,46 @@
         <v>2</v>
       </c>
       <c r="DV9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="DW9" t="n">
         <v>0</v>
       </c>
       <c r="DX9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="DY9" t="n">
         <v>0</v>
       </c>
       <c r="DZ9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="EA9" t="n">
         <v>2</v>
       </c>
       <c r="EB9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EC9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="ED9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="EE9" t="n">
         <v>1</v>
       </c>
       <c r="EF9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="EG9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EH9" t="n">
         <v>2</v>
       </c>
       <c r="EI9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EJ9" t="n">
         <v>0</v>
@@ -4645,22 +4645,22 @@
         <v>2</v>
       </c>
       <c r="EL9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EM9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="EN9" t="n">
         <v>2</v>
       </c>
       <c r="EO9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Victor Bethlem</t>
+          <t>Pedro Thedim</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -4676,19 +4676,19 @@
         <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -4697,10 +4697,10 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -4712,25 +4712,25 @@
         <v>2</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
@@ -4745,13 +4745,13 @@
         <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AF10" t="n">
         <v>5</v>
@@ -4763,34 +4763,34 @@
         <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AM10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AP10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AQ10" t="n">
         <v>1</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS10" t="n">
         <v>0</v>
@@ -4799,28 +4799,28 @@
         <v>2</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV10" t="n">
         <v>1</v>
       </c>
       <c r="AW10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX10" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AY10" t="n">
         <v>0</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA10" t="n">
         <v>1</v>
       </c>
       <c r="BB10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BC10" t="n">
         <v>1</v>
@@ -4844,19 +4844,19 @@
         <v>2</v>
       </c>
       <c r="BJ10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BK10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BL10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BM10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BN10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BO10" t="n">
         <v>0</v>
@@ -4865,19 +4865,19 @@
         <v>0</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BR10" t="n">
         <v>2</v>
       </c>
       <c r="BS10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT10" t="n">
         <v>1</v>
       </c>
       <c r="BU10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BV10" t="n">
         <v>1</v>
@@ -4892,207 +4892,1085 @@
         <v>0</v>
       </c>
       <c r="BZ10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CA10" t="n">
         <v>1</v>
       </c>
       <c r="CB10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CC10" t="n">
         <v>2</v>
       </c>
       <c r="CD10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CF10" t="n">
         <v>0</v>
       </c>
       <c r="CG10" t="n">
+        <v>3</v>
+      </c>
+      <c r="CH10" t="n">
+        <v>6</v>
+      </c>
+      <c r="CI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>2</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>2</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN10" t="n">
+        <v>3</v>
+      </c>
+      <c r="CO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP10" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ10" t="n">
+        <v>3</v>
+      </c>
+      <c r="CR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS10" t="n">
+        <v>1</v>
+      </c>
+      <c r="CT10" t="n">
+        <v>3</v>
+      </c>
+      <c r="CU10" t="n">
+        <v>1</v>
+      </c>
+      <c r="CV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW10" t="n">
+        <v>3</v>
+      </c>
+      <c r="CX10" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ10" t="n">
+        <v>2</v>
+      </c>
+      <c r="DA10" t="n">
+        <v>1</v>
+      </c>
+      <c r="DB10" t="n">
+        <v>2</v>
+      </c>
+      <c r="DC10" t="n">
+        <v>3</v>
+      </c>
+      <c r="DD10" t="n">
+        <v>2</v>
+      </c>
+      <c r="DE10" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF10" t="n">
+        <v>2</v>
+      </c>
+      <c r="DG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH10" t="n">
+        <v>2</v>
+      </c>
+      <c r="DI10" t="n">
+        <v>2</v>
+      </c>
+      <c r="DJ10" t="n">
+        <v>1</v>
+      </c>
+      <c r="DK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL10" t="n">
+        <v>1</v>
+      </c>
+      <c r="DM10" t="n">
+        <v>2</v>
+      </c>
+      <c r="DN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO10" t="n">
+        <v>1</v>
+      </c>
+      <c r="DP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ10" t="n">
+        <v>3</v>
+      </c>
+      <c r="DR10" t="n">
         <v>4</v>
       </c>
-      <c r="CH10" t="n">
-        <v>3</v>
-      </c>
-      <c r="CI10" t="n">
-        <v>0</v>
-      </c>
-      <c r="CJ10" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK10" t="n">
-        <v>2</v>
-      </c>
-      <c r="CL10" t="n">
-        <v>3</v>
-      </c>
-      <c r="CM10" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN10" t="n">
-        <v>1</v>
-      </c>
-      <c r="CO10" t="n">
-        <v>1</v>
-      </c>
-      <c r="CP10" t="n">
-        <v>1</v>
-      </c>
-      <c r="CQ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="CR10" t="n">
-        <v>1</v>
-      </c>
-      <c r="CS10" t="n">
-        <v>2</v>
-      </c>
-      <c r="CT10" t="n">
-        <v>3</v>
-      </c>
-      <c r="CU10" t="n">
-        <v>0</v>
-      </c>
-      <c r="CV10" t="n">
-        <v>1</v>
-      </c>
-      <c r="CW10" t="n">
+      <c r="DS10" t="n">
+        <v>1</v>
+      </c>
+      <c r="DT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU10" t="n">
+        <v>2</v>
+      </c>
+      <c r="DV10" t="n">
+        <v>2</v>
+      </c>
+      <c r="DW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX10" t="n">
+        <v>2</v>
+      </c>
+      <c r="DY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ10" t="n">
+        <v>1</v>
+      </c>
+      <c r="EA10" t="n">
+        <v>2</v>
+      </c>
+      <c r="EB10" t="n">
+        <v>1</v>
+      </c>
+      <c r="EC10" t="n">
+        <v>1</v>
+      </c>
+      <c r="ED10" t="n">
+        <v>1</v>
+      </c>
+      <c r="EE10" t="n">
+        <v>1</v>
+      </c>
+      <c r="EF10" t="n">
+        <v>2</v>
+      </c>
+      <c r="EG10" t="n">
+        <v>2</v>
+      </c>
+      <c r="EH10" t="n">
+        <v>2</v>
+      </c>
+      <c r="EI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EK10" t="n">
+        <v>2</v>
+      </c>
+      <c r="EL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM10" t="n">
+        <v>3</v>
+      </c>
+      <c r="EN10" t="n">
+        <v>1</v>
+      </c>
+      <c r="EO10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Rafael Souto</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="n">
         <v>4</v>
       </c>
-      <c r="CX10" t="n">
-        <v>2</v>
-      </c>
-      <c r="CY10" t="n">
-        <v>0</v>
-      </c>
-      <c r="CZ10" t="n">
-        <v>1</v>
-      </c>
-      <c r="DA10" t="n">
-        <v>1</v>
-      </c>
-      <c r="DB10" t="n">
-        <v>1</v>
-      </c>
-      <c r="DC10" t="n">
-        <v>1</v>
-      </c>
-      <c r="DD10" t="n">
-        <v>3</v>
-      </c>
-      <c r="DE10" t="n">
-        <v>1</v>
-      </c>
-      <c r="DF10" t="n">
-        <v>1</v>
-      </c>
-      <c r="DG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="DH10" t="n">
-        <v>2</v>
-      </c>
-      <c r="DI10" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ10" t="n">
-        <v>2</v>
-      </c>
-      <c r="DK10" t="n">
-        <v>1</v>
-      </c>
-      <c r="DL10" t="n">
-        <v>1</v>
-      </c>
-      <c r="DM10" t="n">
-        <v>3</v>
-      </c>
-      <c r="DN10" t="n">
-        <v>1</v>
-      </c>
-      <c r="DO10" t="n">
-        <v>2</v>
-      </c>
-      <c r="DP10" t="n">
-        <v>0</v>
-      </c>
-      <c r="DQ10" t="n">
-        <v>3</v>
-      </c>
-      <c r="DR10" t="n">
-        <v>1</v>
-      </c>
-      <c r="DS10" t="n">
-        <v>0</v>
-      </c>
-      <c r="DT10" t="n">
-        <v>1</v>
-      </c>
-      <c r="DU10" t="n">
-        <v>2</v>
-      </c>
-      <c r="DV10" t="n">
-        <v>3</v>
-      </c>
-      <c r="DW10" t="n">
-        <v>1</v>
-      </c>
-      <c r="DX10" t="n">
-        <v>2</v>
-      </c>
-      <c r="DY10" t="n">
-        <v>2</v>
-      </c>
-      <c r="DZ10" t="n">
-        <v>1</v>
-      </c>
-      <c r="EA10" t="n">
-        <v>1</v>
-      </c>
-      <c r="EB10" t="n">
-        <v>1</v>
-      </c>
-      <c r="EC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="ED10" t="n">
-        <v>2</v>
-      </c>
-      <c r="EE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="EF10" t="n">
-        <v>1</v>
-      </c>
-      <c r="EG10" t="n">
-        <v>1</v>
-      </c>
-      <c r="EH10" t="n">
-        <v>2</v>
-      </c>
-      <c r="EI10" t="n">
-        <v>0</v>
-      </c>
-      <c r="EJ10" t="n">
-        <v>1</v>
-      </c>
-      <c r="EK10" t="n">
-        <v>1</v>
-      </c>
-      <c r="EL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="EM10" t="n">
-        <v>2</v>
-      </c>
-      <c r="EN10" t="n">
-        <v>1</v>
-      </c>
-      <c r="EO10" t="n">
+      <c r="R11" t="n">
+        <v>2</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1</v>
+      </c>
+      <c r="W11" t="n">
+        <v>2</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>3</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>3</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>2</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>2</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>1</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB11" t="n">
+        <v>1</v>
+      </c>
+      <c r="CC11" t="n">
+        <v>2</v>
+      </c>
+      <c r="CD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE11" t="n">
+        <v>2</v>
+      </c>
+      <c r="CF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG11" t="n">
+        <v>4</v>
+      </c>
+      <c r="CH11" t="n">
+        <v>6</v>
+      </c>
+      <c r="CI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK11" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>3</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN11" t="n">
+        <v>2</v>
+      </c>
+      <c r="CO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ11" t="n">
+        <v>2</v>
+      </c>
+      <c r="CR11" t="n">
+        <v>1</v>
+      </c>
+      <c r="CS11" t="n">
+        <v>4</v>
+      </c>
+      <c r="CT11" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW11" t="n">
+        <v>2</v>
+      </c>
+      <c r="CX11" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY11" t="n">
+        <v>1</v>
+      </c>
+      <c r="CZ11" t="n">
+        <v>2</v>
+      </c>
+      <c r="DA11" t="n">
+        <v>2</v>
+      </c>
+      <c r="DB11" t="n">
+        <v>1</v>
+      </c>
+      <c r="DC11" t="n">
+        <v>2</v>
+      </c>
+      <c r="DD11" t="n">
+        <v>4</v>
+      </c>
+      <c r="DE11" t="n">
+        <v>2</v>
+      </c>
+      <c r="DF11" t="n">
+        <v>2</v>
+      </c>
+      <c r="DG11" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH11" t="n">
+        <v>4</v>
+      </c>
+      <c r="DI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ11" t="n">
+        <v>1</v>
+      </c>
+      <c r="DK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM11" t="n">
+        <v>1</v>
+      </c>
+      <c r="DN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO11" t="n">
+        <v>1</v>
+      </c>
+      <c r="DP11" t="n">
+        <v>2</v>
+      </c>
+      <c r="DQ11" t="n">
+        <v>6</v>
+      </c>
+      <c r="DR11" t="n">
+        <v>7</v>
+      </c>
+      <c r="DS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU11" t="n">
+        <v>2</v>
+      </c>
+      <c r="DV11" t="n">
+        <v>4</v>
+      </c>
+      <c r="DW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX11" t="n">
+        <v>5</v>
+      </c>
+      <c r="DY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA11" t="n">
+        <v>2</v>
+      </c>
+      <c r="EB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC11" t="n">
+        <v>2</v>
+      </c>
+      <c r="ED11" t="n">
+        <v>3</v>
+      </c>
+      <c r="EE11" t="n">
+        <v>1</v>
+      </c>
+      <c r="EF11" t="n">
+        <v>3</v>
+      </c>
+      <c r="EG11" t="n">
+        <v>1</v>
+      </c>
+      <c r="EH11" t="n">
+        <v>2</v>
+      </c>
+      <c r="EI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EK11" t="n">
+        <v>2</v>
+      </c>
+      <c r="EL11" t="n">
+        <v>1</v>
+      </c>
+      <c r="EM11" t="n">
+        <v>6</v>
+      </c>
+      <c r="EN11" t="n">
+        <v>2</v>
+      </c>
+      <c r="EO11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Victor Bethlem</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>3</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>2</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>3</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>2</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>2</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>1</v>
+      </c>
+      <c r="CB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC12" t="n">
+        <v>2</v>
+      </c>
+      <c r="CD12" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE12" t="n">
+        <v>2</v>
+      </c>
+      <c r="CF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG12" t="n">
+        <v>4</v>
+      </c>
+      <c r="CH12" t="n">
+        <v>3</v>
+      </c>
+      <c r="CI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ12" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK12" t="n">
+        <v>2</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>3</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN12" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO12" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP12" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR12" t="n">
+        <v>1</v>
+      </c>
+      <c r="CS12" t="n">
+        <v>2</v>
+      </c>
+      <c r="CT12" t="n">
+        <v>3</v>
+      </c>
+      <c r="CU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV12" t="n">
+        <v>1</v>
+      </c>
+      <c r="CW12" t="n">
+        <v>4</v>
+      </c>
+      <c r="CX12" t="n">
+        <v>2</v>
+      </c>
+      <c r="CY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ12" t="n">
+        <v>1</v>
+      </c>
+      <c r="DA12" t="n">
+        <v>1</v>
+      </c>
+      <c r="DB12" t="n">
+        <v>1</v>
+      </c>
+      <c r="DC12" t="n">
+        <v>1</v>
+      </c>
+      <c r="DD12" t="n">
+        <v>3</v>
+      </c>
+      <c r="DE12" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF12" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH12" t="n">
+        <v>2</v>
+      </c>
+      <c r="DI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ12" t="n">
+        <v>2</v>
+      </c>
+      <c r="DK12" t="n">
+        <v>1</v>
+      </c>
+      <c r="DL12" t="n">
+        <v>1</v>
+      </c>
+      <c r="DM12" t="n">
+        <v>3</v>
+      </c>
+      <c r="DN12" t="n">
+        <v>1</v>
+      </c>
+      <c r="DO12" t="n">
+        <v>2</v>
+      </c>
+      <c r="DP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ12" t="n">
+        <v>3</v>
+      </c>
+      <c r="DR12" t="n">
+        <v>1</v>
+      </c>
+      <c r="DS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT12" t="n">
+        <v>1</v>
+      </c>
+      <c r="DU12" t="n">
+        <v>2</v>
+      </c>
+      <c r="DV12" t="n">
+        <v>3</v>
+      </c>
+      <c r="DW12" t="n">
+        <v>1</v>
+      </c>
+      <c r="DX12" t="n">
+        <v>2</v>
+      </c>
+      <c r="DY12" t="n">
+        <v>2</v>
+      </c>
+      <c r="DZ12" t="n">
+        <v>1</v>
+      </c>
+      <c r="EA12" t="n">
+        <v>1</v>
+      </c>
+      <c r="EB12" t="n">
+        <v>1</v>
+      </c>
+      <c r="EC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED12" t="n">
+        <v>2</v>
+      </c>
+      <c r="EE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF12" t="n">
+        <v>1</v>
+      </c>
+      <c r="EG12" t="n">
+        <v>1</v>
+      </c>
+      <c r="EH12" t="n">
+        <v>2</v>
+      </c>
+      <c r="EI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ12" t="n">
+        <v>1</v>
+      </c>
+      <c r="EK12" t="n">
+        <v>1</v>
+      </c>
+      <c r="EL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM12" t="n">
+        <v>2</v>
+      </c>
+      <c r="EN12" t="n">
+        <v>1</v>
+      </c>
+      <c r="EO12" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5107,7 +5985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM10"/>
+  <dimension ref="A1:BM12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5440,10 +6318,10 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Leonardo Martins</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
+          <t>Ana Beatriz Ferreira</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -5468,7 +6346,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -5488,12 +6366,12 @@
           <t>X</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -5573,7 +6451,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="BB2" t="inlineStr">
+      <c r="BC2" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -5607,174 +6485,174 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Pedro Brandão</t>
+          <t>Leonardo Martins</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>x</t>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>x</t>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>x</t>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>x</t>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Rafaela Albano Ribeiro</t>
+          <t>Mariella Lage</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -5787,7 +6665,7 @@
           <t>x</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -5827,7 +6705,7 @@
           <t>x</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -5842,7 +6720,7 @@
           <t>x</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -5877,7 +6755,7 @@
           <t>x</t>
         </is>
       </c>
-      <c r="AQ4" t="inlineStr">
+      <c r="AP4" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -5887,7 +6765,7 @@
           <t>x</t>
         </is>
       </c>
-      <c r="AT4" t="inlineStr">
+      <c r="AU4" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -5912,7 +6790,7 @@
           <t>x</t>
         </is>
       </c>
-      <c r="BD4" t="inlineStr">
+      <c r="BE4" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -5941,341 +6819,341 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ana Leticia Xavier</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>X</t>
+          <t>Pedro Brandão</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>x</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>X</t>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>x</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>x</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>x</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>x</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>x</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>x</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>x</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>x</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>x</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>x</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>x</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>x</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>x</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>x</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>x</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>x</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>x</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>x</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>X</t>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>x</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>x</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>x</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>x</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="BC5" t="inlineStr">
-        <is>
-          <t>X</t>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>x</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="BF5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>X</t>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>x</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>x</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>x</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Gustavo Marini</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>X</t>
+          <t>Rafaela Albano Ribeiro</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>x</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>X</t>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>x</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>x</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>X</t>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>x</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>x</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>x</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>x</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>x</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>x</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>x</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>x</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>x</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>x</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>X</t>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>x</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>x</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>x</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>x</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>X</t>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>x</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>x</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>x</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>x</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>x</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="BE6" t="inlineStr">
-        <is>
-          <t>X</t>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>x</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>x</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>x</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>x</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>x</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Marcio</t>
+          <t>Ana Leticia Xavier</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -6288,7 +7166,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -6383,7 +7261,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="AS7" t="inlineStr">
+      <c r="AR7" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -6408,7 +7286,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="BB7" t="inlineStr">
+      <c r="BC7" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -6418,12 +7296,12 @@
           <t>X</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="BI7" t="inlineStr">
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -6442,7 +7320,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Pedro Thedim</t>
+          <t>Gustavo Marini</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -6455,7 +7333,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -6470,12 +7348,12 @@
           <t>X</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -6495,7 +7373,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -6510,7 +7388,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -6522,419 +7400,753 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>x</t>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="BF8" t="inlineStr">
-        <is>
-          <t>x</t>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="BK8" t="inlineStr">
-        <is>
-          <t>x</t>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Rafael Souto</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>x</t>
+          <t>Marcio</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>x</t>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>x</t>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>x</t>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="BC9" t="inlineStr">
-        <is>
-          <t>x</t>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="BF9" t="inlineStr">
-        <is>
-          <t>x</t>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>X</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Pedro Thedim</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="BK10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="BM10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Rafael Souto</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="BJ11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="BL11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>Victor Bethlem</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="BB10" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="BE10" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="BI10" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="BJ10" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="BM10" t="inlineStr">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="BJ12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="BM12" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -6951,7 +8163,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6974,24 +8186,24 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Leonardo Martins</t>
+          <t>Ana Beatriz Ferreira</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kylian Mbappé</t>
+          <t>Harry Kane</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>Alemanha</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Pedro Brandão</t>
+          <t>Leonardo Martins</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -7008,24 +8220,24 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Rafaela Albano Ribeiro</t>
+          <t>Mariella Lage</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Julián Álvarez</t>
+          <t>Harry Kane</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Brasil</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ana Leticia Xavier</t>
+          <t>Pedro Brandão</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -7042,29 +8254,29 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Gustavo Marini</t>
+          <t>Rafaela Albano Ribeiro</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Danilo Santos</t>
+          <t>Julián Álvarez</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Argentina</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Marcio</t>
+          <t>Ana Leticia Xavier</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Harry Kane</t>
+          <t>Kylian Mbappé</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -7076,49 +8288,83 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Pedro Thedim</t>
+          <t>Gustavo Marini</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Kylian Mbappé</t>
+          <t>Danilo Santos</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Franca</t>
+          <t>Brasil</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Rafael Souto</t>
+          <t>Marcio</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Julián Álvarez</t>
+          <t>Harry Kane</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Espanha</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Pedro Thedim</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kylian Mbappé</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Franca</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Rafael Souto</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Julián Álvarez</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>Victor Bethlem</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Kylian Mbappé</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Inglaterra</t>
         </is>

--- a/apostas/Bolao_Copa2026_TurimMFO - Consolidada.xlsx
+++ b/apostas/Bolao_Copa2026_TurimMFO - Consolidada.xlsx
@@ -44101,9 +44101,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>X</t>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>x</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
